--- a/tatort_verfuegbarkeit.xlsx
+++ b/tatort_verfuegbarkeit.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ARD_Mediathek</t>
+          <t>ARD_availableTo</t>
         </is>
       </c>
     </row>
@@ -488,9 +488,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-heute-aus-rostock-die-angst-heiligt-die-mittel-mit-charly-huebner-a-1127899.html</t>
         </is>
       </c>
-      <c r="G2" t="b">
-        <v>0</v>
-      </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,9 +517,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-heute-aus-magdeburg-black-box-im-schnellcheck-a-4f9c04fa-630c-440e-952e-e425c8d316c1</t>
         </is>
       </c>
-      <c r="G3" t="b">
-        <v>0</v>
-      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -546,9 +542,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-cottbus-kopflos-im-schnellcheck-a-3dada17d-8e17-4def-9c8e-531f9cbb2345</t>
         </is>
       </c>
-      <c r="G4" t="b">
-        <v>0</v>
-      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -577,9 +571,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-aus-magdeburg-crash-im-schnellcheck-a-1226662.html</t>
         </is>
       </c>
-      <c r="G5" t="b">
-        <v>0</v>
-      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -608,9 +600,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-aus-rostock-daniel-a-im-schnellcheck-a-9299ba83-103f-49b3-b32f-4dad064fa9cb</t>
         </is>
       </c>
-      <c r="G6" t="b">
-        <v>0</v>
-      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -639,9 +629,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-aus-brandenburg-das-beste-fuer-mein-kind-im-check-a-1180472.html</t>
         </is>
       </c>
-      <c r="G7" t="b">
-        <v>0</v>
-      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -670,9 +658,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-aus-muenchen-das-gespenst-der-freiheit-im-check-a-1223126.html</t>
         </is>
       </c>
-      <c r="G8" t="b">
-        <v>0</v>
-      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -701,9 +687,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-aus-muenchen-das-licht-das-die-toten-sehen-im-schnellcheck-a-a9b928ab-7ac5-4743-a5d2-a1c800c48e75</t>
         </is>
       </c>
-      <c r="G9" t="b">
-        <v>0</v>
-      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -728,9 +712,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-demokratie-stirbt-in-finsternis-im-schnellcheck-a-1203289.html</t>
         </is>
       </c>
-      <c r="G10" t="b">
-        <v>0</v>
-      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -755,9 +737,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-mit-peter-kurth-der-dicke-liebt-im-schnellcheck-a-9c93b98c-4d4e-44ca-ad06-5755b63d3e19</t>
         </is>
       </c>
-      <c r="G11" t="b">
-        <v>0</v>
-      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -786,9 +766,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-heute-aus-muenchen-mit-verena-altenberger-schnellcheck-a-1285063.html</t>
         </is>
       </c>
-      <c r="G12" t="b">
-        <v>0</v>
-      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -813,9 +791,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-mit-maria-simon-der-schnellcheck-a-1087379.html</t>
         </is>
       </c>
-      <c r="G13" t="b">
-        <v>0</v>
-      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -844,9 +820,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-aus-rostock-der-tag-wird-kommen-im-schnellcheck-a-5c20f19e-11a7-43d7-958d-b2187d7d239e</t>
         </is>
       </c>
-      <c r="G14" t="b">
-        <v>0</v>
-      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -875,9 +849,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-aus-magdeburg-der-verurteilte-im-schnellcheck-a-577d1b7f-d9f6-4308-ab68-9cbf9fbf19cd</t>
         </is>
       </c>
-      <c r="G15" t="b">
-        <v>0</v>
-      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -906,9 +878,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-aus-muenchen-im-schnellcheck-a-1298020.html</t>
         </is>
       </c>
-      <c r="G16" t="b">
-        <v>0</v>
-      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -933,9 +903,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-der-ard-sonntagskrimi-im-schnellcheck-a-cd88bed7-6c1d-4bc4-afec-255ad689b583</t>
         </is>
       </c>
-      <c r="G17" t="b">
-        <v>0</v>
-      </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -964,9 +932,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-aus-rockstock-einer-fuer-alle-alle-fuer-rostock-im-check-a-1145532.html</t>
         </is>
       </c>
-      <c r="G18" t="b">
-        <v>0</v>
-      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -995,9 +961,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-aus-muenchen-frau-schroedingers-katze-im-schnellcheck-a-9f861e3d-dff2-430d-b5b7-c216774fe412</t>
         </is>
       </c>
-      <c r="G19" t="b">
-        <v>0</v>
-      </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1026,9 +990,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-heute-aus-muenchen-funkensommer-im-schnellcheck-a-2247ee61-fea0-4069-a796-c394d4416fcb</t>
         </is>
       </c>
-      <c r="G20" t="b">
-        <v>0</v>
-      </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1057,9 +1019,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-aus-rostock-fuer-janina-im-schnellcheck-a-1234405.html</t>
         </is>
       </c>
-      <c r="G21" t="b">
-        <v>0</v>
-      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1084,9 +1044,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-mit-maria-simon-heilig-sollt-ihr-sein-im-schnellcheck-a-61adc2bd-2da8-45a9-820a-518eca5276fa</t>
         </is>
       </c>
-      <c r="G22" t="b">
-        <v>0</v>
-      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1111,9 +1069,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-mit-lucas-gregorowicz-hermann-im-schnellcheck-a-b76ec970-e177-48b6-ba54-dfcfcb868420</t>
         </is>
       </c>
-      <c r="G23" t="b">
-        <v>0</v>
-      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1138,9 +1094,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-heute-mit-gregorowicz-und-kaczmarczyk-hildes-erbe-im-schnellcheck-a-30658a0b-e7e2-40cf-9239-bb617ca6960c</t>
         </is>
       </c>
-      <c r="G24" t="b">
-        <v>0</v>
-      </c>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1169,9 +1123,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-aus-rostock-im-schatten-im-schnellcheck-a-1115437.html</t>
         </is>
       </c>
-      <c r="G25" t="b">
-        <v>0</v>
-      </c>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1200,9 +1152,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-heute-aus-rostock-der-abschied-von-huebner-als-bukow-im-schnellcheck-a-18a8eb44-4db0-41d6-922a-d273f14440b3</t>
         </is>
       </c>
-      <c r="G26" t="b">
-        <v>0</v>
-      </c>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1231,9 +1181,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-aus-rostock-kindeswohl-im-schnellcheck-a-1261045.html</t>
         </is>
       </c>
-      <c r="G27" t="b">
-        <v>0</v>
-      </c>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1258,9 +1206,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-mit-johanna-wokalek-little-boxes-im-schnellcheck-a-34a71732-2807-4246-9192-deb1b1f0968d</t>
         </is>
       </c>
-      <c r="G28" t="b">
-        <v>0</v>
-      </c>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1285,9 +1231,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-monstermutter-im-schnellcheck-a-81244d44-afc2-4a02-8487-d76eb9ee4b7e</t>
         </is>
       </c>
-      <c r="G29" t="b">
-        <v>0</v>
-      </c>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1316,9 +1260,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-heute-aus-magdeburg-moerderische-dorfgemeinschaft-im-schnellcheck-a-1278850.html</t>
         </is>
       </c>
-      <c r="G30" t="b">
-        <v>0</v>
-      </c>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1347,9 +1289,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-heute-aus-brandenburg-muttertag-mit-maria-simon-im-schnellcheck-a-1146442.html</t>
         </is>
       </c>
-      <c r="G31" t="b">
-        <v>0</v>
-      </c>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1378,9 +1318,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-heute-aus-muenchen-nachtdienst-mit-matthias-brandt-im-check-a-1140935.html</t>
         </is>
       </c>
-      <c r="G32" t="b">
-        <v>0</v>
-      </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1409,9 +1347,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-aus-rostock-nur-gespenster-im-schnellcheck-a-5f15e89d-55c9-4372-a62f-00be2aa74c16</t>
         </is>
       </c>
-      <c r="G33" t="b">
-        <v>0</v>
-      </c>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1436,9 +1372,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-heute-mit-verena-altenberger-paranoia-im-schnellcheck-a-6a727fda-45b8-4273-923a-f49d068e5932</t>
         </is>
       </c>
-      <c r="G34" t="b">
-        <v>0</v>
-      </c>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1467,9 +1401,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-heute-aus-magdeburg-ronny-im-schnellcheck-a-b2d209f2-c509-47de-b272-9c3784a50020</t>
         </is>
       </c>
-      <c r="G35" t="b">
-        <v>0</v>
-      </c>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1498,9 +1430,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-aus-rostock-sabine-im-schnellcheck-a-0694eb1d-7d02-48d9-8285-eb1727ee63a2</t>
         </is>
       </c>
-      <c r="G36" t="b">
-        <v>0</v>
-      </c>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1525,9 +1455,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-mit-gisa-flake-schweine-im-schnellcheck-a-aadb6c9b-0e94-49e1-9d69-17a9ed3dff39</t>
         </is>
       </c>
-      <c r="G37" t="b">
-        <v>0</v>
-      </c>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1556,9 +1484,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-heute-aus-rostock-im-schnellcheck-anneke-kim-sarnau-im-team-mit-lina-beckmann-a-fdcb4d9a-ec70-4702-9a56-c72a9ee3e239</t>
         </is>
       </c>
-      <c r="G38" t="b">
-        <v>0</v>
-      </c>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1587,9 +1513,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-aus-rostock-soehne-rostocks-im-schnellcheck-a-27b6dc6f-df31-4c3e-8575-80b7b032a232</t>
         </is>
       </c>
-      <c r="G39" t="b">
-        <v>0</v>
-      </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1614,9 +1538,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-von-der-oder-spiel-gegen-den-ball-im-schnellcheck-a-a0de9d7a-b534-4968-9c7b-834f75bbf944</t>
         </is>
       </c>
-      <c r="G40" t="b">
-        <v>0</v>
-      </c>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1645,9 +1567,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-aus-magdeburg-starke-schultern-im-schnellcheck-a-1198942.html</t>
         </is>
       </c>
-      <c r="G41" t="b">
-        <v>0</v>
-      </c>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1672,9 +1592,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-mit-matthias-brandt-tatorte-im-schnellcheck-a-1241815.html</t>
         </is>
       </c>
-      <c r="G42" t="b">
-        <v>0</v>
-      </c>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1699,9 +1617,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-mit-maria-simon-tod-einer-journalistin-im-check-a-1299488.html</t>
         </is>
       </c>
-      <c r="G43" t="b">
-        <v>0</v>
-      </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1730,9 +1646,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-aus-magdeburg-tod-einer-toten-im-schnellcheck-a-3a5d9f9b-ea77-4657-8da1-a8ebc8d9daf1</t>
         </is>
       </c>
-      <c r="G44" t="b">
-        <v>0</v>
-      </c>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1761,9 +1675,7 @@
           <t>https://www.spiegel.de/kultur/tv/der-polizeiruf-heute-aus-magdeburg-totes-rennen-im-schnellcheck-a-5cccd13f-f807-4380-ba69-438df9261b8e</t>
         </is>
       </c>
-      <c r="G45" t="b">
-        <v>0</v>
-      </c>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1788,9 +1700,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-mit-andre-kaczmarczyk-wasserwege-im-schnellcheck-a-c056ccc2-f713-44ec-a073-9c9a7edda504</t>
         </is>
       </c>
-      <c r="G46" t="b">
-        <v>0</v>
-      </c>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1819,9 +1729,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-aus-magdeburg-widerfahrnis-im-schnellcheck-a-25ad3db0-3554-4030-9978-8ea4a63e5674</t>
         </is>
       </c>
-      <c r="G47" t="b">
-        <v>0</v>
-      </c>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1846,9 +1754,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-woelfe-mit-matthias-brandt-schnellcheck-a-1110266.html</t>
         </is>
       </c>
-      <c r="G48" t="b">
-        <v>0</v>
-      </c>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1873,9 +1779,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-heute-mit-lucas-gregorowicz-abgrund-im-schnellcheck-a-3ae72a91-0954-4baf-ab2e-74967f2ce880</t>
         </is>
       </c>
-      <c r="G49" t="b">
-        <v>0</v>
-      </c>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1904,9 +1808,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-aus-halle-an-der-saale-hellem-strande-im-schnellcheck-a-ad71d310-a3fc-4a84-870f-b1f73467fd7a</t>
         </is>
       </c>
-      <c r="G50" t="b">
-        <v>0</v>
-      </c>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1935,9 +1837,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-heute-aus-rostock-boese-geboren-im-schnellcheck-a-7a13bd46-f982-424e-b50d-dc48477adbed</t>
         </is>
       </c>
-      <c r="G51" t="b">
-        <v>0</v>
-      </c>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1966,9 +1866,7 @@
           <t>https://www.spiegel.de/kultur/literatur/polizeiruf-110-heute-aus-magdeburg-du-gehoerst-mir-im-schnellcheck-a-252fcef0-6cce-4da9-a4f1-bf90db1a3bfd</t>
         </is>
       </c>
-      <c r="G52" t="b">
-        <v>0</v>
-      </c>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1997,9 +1895,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-aus-magdeburg-endstation-mit-matthias-matschke-und-claudia-michelsen-im-schnellcheck-a-1093809.html</t>
         </is>
       </c>
-      <c r="G53" t="b">
-        <v>0</v>
-      </c>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2028,9 +1924,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-aus-magdeburg-sie-sind-unter-uns-im-schnellcheck-a-77ef0958-70ff-41d9-8c4d-e852fdd170ee</t>
         </is>
       </c>
-      <c r="G54" t="b">
-        <v>0</v>
-      </c>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2059,9 +1953,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-heute-aus-rostock-tu-es-mit-lina-beckmann-im-schnellcheck-a-20db9a79-5c84-4bb1-bc09-36a2114f037f</t>
         </is>
       </c>
-      <c r="G55" t="b">
-        <v>0</v>
-      </c>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2090,9 +1982,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-aus-muenchen-mit-matthias-brandt-der-check-a-1070277.html</t>
         </is>
       </c>
-      <c r="G56" t="b">
-        <v>0</v>
-      </c>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2121,9 +2011,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-heute-aus-magdeburg-unsterblich-im-schnellcheck-a-8f71219b-4562-4210-bf62-6f893e582fc1</t>
         </is>
       </c>
-      <c r="G57" t="b">
-        <v>0</v>
-      </c>
+      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2152,8 +2040,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-abbruchkante-im-schnellcheck-a-5fcccf19-cf69-4091-b75b-eb17f37a07d1</t>
         </is>
       </c>
-      <c r="G58" t="b">
-        <v>1</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-09-01T21:10:00Z</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -2183,8 +2073,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dortmund-abstellgleis-im-schnellcheck-a-06f3b1f6-cd73-4e2d-81cf-42902e4b0991</t>
         </is>
       </c>
-      <c r="G59" t="b">
-        <v>1</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-03-30T18:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -2214,9 +2106,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dem-schwarzwald-ad-acta-mit-tobler-und-berg-im-schnellcheck-a-f8bc6d72-0457-41c5-938f-6f77127a6d38</t>
         </is>
       </c>
-      <c r="G60" t="b">
-        <v>0</v>
-      </c>
+      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2245,9 +2135,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-hamburg-mit-maria-furtwaengler-alles-kommt-zurueck-im-schnellcheck-a-30b84cec-95f0-46ad-b12a-b3fe4ce5d21b</t>
         </is>
       </c>
-      <c r="G61" t="b">
-        <v>0</v>
-      </c>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2276,8 +2164,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-wien-alles-was-recht-ist-im-schnellcheck-a-a2ac47b8-8093-4efe-9992-2611dc8bac38</t>
         </is>
       </c>
-      <c r="G62" t="b">
-        <v>1</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-08-14T12:30:00Z</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -2303,9 +2193,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-falke-alles-was-sie-sagen-im-schnellcheck-a-1202514.html</t>
         </is>
       </c>
-      <c r="G63" t="b">
-        <v>0</v>
-      </c>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2334,8 +2222,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-franken-am-ende-geht-man-nackt-im-schnellcheck-a-1141139.html</t>
         </is>
       </c>
-      <c r="G64" t="b">
-        <v>1</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-04-30T21:30:00Z</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -2365,9 +2255,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-berlin-am-tag-der-wandernden-seelen-im-schnellcheck-a-f7fd6bf6-ce04-4e44-99aa-705c84026713</t>
         </is>
       </c>
-      <c r="G65" t="b">
-        <v>0</v>
-      </c>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2396,9 +2284,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-berlin-amour-fou-im-schnellcheck-a-1148118.html</t>
         </is>
       </c>
-      <c r="G66" t="b">
-        <v>0</v>
-      </c>
+      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2423,8 +2309,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-ulrich-tukur-angriff-auf-wache-08-im-schnellcheck-a-1289670.html</t>
         </is>
       </c>
-      <c r="G67" t="b">
-        <v>1</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-10-22T20:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -2454,8 +2342,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-bremen-angst-im-dunkeln-im-schnellcheck-a-1467d759-4ab6-4957-b4c0-6acfceb6c61b</t>
         </is>
       </c>
-      <c r="G68" t="b">
-        <v>1</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:40:00Z</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -2485,9 +2375,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-wiederholung-heute-aus-stuttgart-anne-und-der-tod-im-schnellcheck-a-d2fc3b6c-8713-41da-9848-7837afd497a8</t>
         </is>
       </c>
-      <c r="G69" t="b">
-        <v>0</v>
-      </c>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2516,9 +2404,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-stuttgart-anne-und-der-tod-im-schnellcheck-a-1266209.html</t>
         </is>
       </c>
-      <c r="G70" t="b">
-        <v>0</v>
-      </c>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2547,9 +2433,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-stuttgart-anne-und-der-tod-im-schnellcheck-a-a399e2bd-7c8f-4384-bedf-94d36278eefc</t>
         </is>
       </c>
-      <c r="G71" t="b">
-        <v>0</v>
-      </c>
+      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2578,9 +2462,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dresden-so-schlaegt-sich-das-neue-team-schnellcheck-a-1077911.html</t>
         </is>
       </c>
-      <c r="G72" t="b">
-        <v>0</v>
-      </c>
+      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2609,9 +2491,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dresden-auge-um-auge-mit-martin-brambach-im-check-a-1176822.html</t>
         </is>
       </c>
-      <c r="G73" t="b">
-        <v>0</v>
-      </c>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2640,9 +2520,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-der-schweiz-ausgezaehlt-im-schnellcheck-a-1272119.html</t>
         </is>
       </c>
-      <c r="G74" t="b">
-        <v>0</v>
-      </c>
+      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2667,9 +2545,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-odenthal-und-stern-avatar-im-schnellcheck-a-0e571c42-0f82-4272-bfb3-af51463dfe96</t>
         </is>
       </c>
-      <c r="G75" t="b">
-        <v>0</v>
-      </c>
+      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2698,9 +2574,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-wien-azra-mit-eisner-und-fellner-im-schnellcheck-a-5acf12c4-ab8c-45f4-9756-f8a1810c6e36</t>
         </is>
       </c>
-      <c r="G76" t="b">
-        <v>0</v>
-      </c>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2729,9 +2603,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-ludwigshafen-babbeldasch-im-schnellcheck-a-1135206.html</t>
         </is>
       </c>
-      <c r="G77" t="b">
-        <v>0</v>
-      </c>
+      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2760,9 +2632,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-wien-bauernsterben-im-schnellcheck-a-d7e1c2f0-d583-4a81-8337-3efe08d6fc7e</t>
         </is>
       </c>
-      <c r="G78" t="b">
-        <v>0</v>
-      </c>
+      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2793,9 +2663,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-oesterreich-baum-faellt-im-schnellcheck-a-1296900.html</t>
         </is>
       </c>
-      <c r="G79" t="b">
-        <v>0</v>
-      </c>
+      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2824,9 +2692,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-bausuenden-im-schnellcheck-a-1188243.html</t>
         </is>
       </c>
-      <c r="G80" t="b">
-        <v>0</v>
-      </c>
+      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2855,9 +2721,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-zuerich-blinder-fleck-im-schnellcheck-a-0a19658e-dd4e-42f8-b701-7b97ff64cf47</t>
         </is>
       </c>
-      <c r="G81" t="b">
-        <v>0</v>
-      </c>
+      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2886,9 +2750,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-bremen-blut-im-schnellcheck-a-1230751.html</t>
         </is>
       </c>
-      <c r="G82" t="b">
-        <v>0</v>
-      </c>
+      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2917,9 +2779,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-bombengeschaeft-im-schnellcheck-a-1258130.html</t>
         </is>
       </c>
-      <c r="G83" t="b">
-        <v>0</v>
-      </c>
+      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2948,9 +2808,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-kiel-borowski-und-das-dunkle-netz-uebers-darknet-a-1138151.html</t>
         </is>
       </c>
-      <c r="G84" t="b">
-        <v>0</v>
-      </c>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2979,8 +2837,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-kiel-borowski-und-das-ewige-meer-im-schnellcheck-a-4c6e885a-5d3f-4d6f-94d7-0898833feae3</t>
         </is>
       </c>
-      <c r="G85" t="b">
-        <v>1</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-02-04T21:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -3010,9 +2870,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-kiel-das-glueck-der-anderen-im-schnellcheck-a-1254152.html</t>
         </is>
       </c>
-      <c r="G86" t="b">
-        <v>0</v>
-      </c>
+      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3041,8 +2899,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-kiel-borowski-und-das-haupt-der-medusa-im-schnellcheck-a-a290acb8-da1a-4789-b08b-4e42343a4361</t>
         </is>
       </c>
-      <c r="G87" t="b">
-        <v>1</v>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-12-09T21:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -3072,9 +2932,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-kiel-borowski-und-das-haus-der-geister-im-schnellcheck-a-1224206.html</t>
         </is>
       </c>
-      <c r="G88" t="b">
-        <v>0</v>
-      </c>
+      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3103,8 +2961,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-kiel-borowski-und-das-hungrige-herz-im-schnellcheck-a-cf800450-eaf6-4b3f-b2bf-d6908f3f3e6f</t>
         </is>
       </c>
-      <c r="G89" t="b">
-        <v>1</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-07-06T18:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -3134,9 +2994,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-kiel-das-land-zwischen-den-meeren-im-schnellcheck-a-1193715.html</t>
         </is>
       </c>
-      <c r="G90" t="b">
-        <v>0</v>
-      </c>
+      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3161,9 +3019,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-borowski-und-das-unschuldige-kind-von-wacken-im-schnellcheck-a-dcc1192a-d2d1-4b0d-b3f6-31b683438bda</t>
         </is>
       </c>
-      <c r="G91" t="b">
-        <v>0</v>
-      </c>
+      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3192,9 +3048,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-kiel-der-schnellcheck-a-1119509.html</t>
         </is>
       </c>
-      <c r="G92" t="b">
-        <v>0</v>
-      </c>
+      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3223,9 +3077,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-kiel-borowski-und-der-gute-mensch-im-schnellcheck-a-c30d1f90-0265-4323-bc6d-b8e76fc18604</t>
         </is>
       </c>
-      <c r="G93" t="b">
-        <v>0</v>
-      </c>
+      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3254,9 +3106,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-kiel-borowski-und-der-schatten-des-mondes-im-schnellcheck-a-0d8c2910-ae57-46b4-bdc8-2087d619d76a</t>
         </is>
       </c>
-      <c r="G94" t="b">
-        <v>0</v>
-      </c>
+      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3285,8 +3135,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-kiel-borowski-und-der-wiedergaenger-im-schnellcheck-a-5fd896f6-9eb7-4953-ab08-7ea8a66c25ef</t>
         </is>
       </c>
-      <c r="G95" t="b">
-        <v>1</v>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-07-03T18:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -3316,9 +3168,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-kiel-borowski-und-die-angst-der-weissen-maenner-im-schnellcheck-a-fc784aee-81a1-429c-a3e0-8b0cdd14157c</t>
         </is>
       </c>
-      <c r="G96" t="b">
-        <v>0</v>
-      </c>
+      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3347,9 +3197,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-kiel-borowski-und-die-angst-der-weissen-maenner-im-schnellcheck-a-ee1b9bd6-cc46-4b10-8e1e-60d63c3a3efd</t>
         </is>
       </c>
-      <c r="G97" t="b">
-        <v>0</v>
-      </c>
+      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3378,9 +3226,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-kiel-borowski-und-die-grosse-wut-im-schnellcheck-a-7c82011c-d011-4d4d-9663-00760af6a47b</t>
         </is>
       </c>
-      <c r="G98" t="b">
-        <v>0</v>
-      </c>
+      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3405,9 +3251,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-kommissar-falke-boeser-boden-im-schnellcheck-a-1179840.html</t>
         </is>
       </c>
-      <c r="G99" t="b">
-        <v>0</v>
-      </c>
+      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3436,9 +3280,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dortmund-cash-mit-joerg-hartmann-im-schnellcheck-a-54c17da1-0c03-43fa-81ba-f3a70118bf95</t>
         </is>
       </c>
-      <c r="G100" t="b">
-        <v>0</v>
-      </c>
+      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3467,8 +3309,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenchen-charlie-im-schnellcheck-a-89fff808-7851-4d91-88f3-b8f5a16b2080</t>
         </is>
       </c>
-      <c r="G101" t="b">
-        <v>1</v>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026-03-02T17:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -3498,8 +3342,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-colonius-im-schnellcheck-a-cac656e3-5ac1-4f88-a6dc-3633b53b7f35</t>
         </is>
       </c>
-      <c r="G102" t="b">
-        <v>1</v>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026-07-13T19:40:00Z</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -3529,9 +3375,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dem-schwarzwald-damian-im-schnellcheck-a-1241816.html</t>
         </is>
       </c>
-      <c r="G103" t="b">
-        <v>0</v>
-      </c>
+      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3560,9 +3404,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dem-schwarzwald-damian-im-schnellcheck-a-50b86589-8941-49d4-bf5c-59ba5d3805b6</t>
         </is>
       </c>
-      <c r="G104" t="b">
-        <v>0</v>
-      </c>
+      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3591,8 +3433,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-saarbruecken-das-ende-der-nacht-im-schnellcheck-a-5ec81325-9e54-4dc3-9704-067d80eeafd2</t>
         </is>
       </c>
-      <c r="G105" t="b">
-        <v>1</v>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2027-01-04T22:59:00Z</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -3622,8 +3466,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-saarbruecken-das-fleissige-lieschen-im-schnellcheck-a-549ff759-cf0b-4bee-9ec5-0dd11c12f404</t>
         </is>
       </c>
-      <c r="G106" t="b">
-        <v>1</v>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2026-01-28T21:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -3653,9 +3499,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dem-schwarzwald-das-geheime-leben-unserer-kinder-im-schnellcheck-a-dda873eb-f12c-4d40-bd88-5ad61439a2b1</t>
         </is>
       </c>
-      <c r="G107" t="b">
-        <v>0</v>
-      </c>
+      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3684,9 +3528,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-kiel-borowski-und-das-haus-am-meer-im-check-a-1299079.html</t>
         </is>
       </c>
-      <c r="G108" t="b">
-        <v>0</v>
-      </c>
+      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3715,8 +3557,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-saarbruecken-das-herz-der-schlange-im-schnellcheck-a-969ab65c-17de-41e1-8dad-8aa9f6c323ef</t>
         </is>
       </c>
-      <c r="G109" t="b">
-        <v>1</v>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2026-12-29T22:59:00Z</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -3746,8 +3590,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-stuttgart-das-ist-unser-haus-im-schnellcheck-a-67314d65-5bf6-4967-ad97-1f0559654bdb</t>
         </is>
       </c>
-      <c r="G110" t="b">
-        <v>1</v>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2027-01-13T22:59:00Z</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -3777,8 +3623,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dem-schwarzwald-das-juengste-geisslein-im-schnellcheck-a-f08c00d2-da34-4ce5-bf8d-4216757b35f3</t>
         </is>
       </c>
-      <c r="G111" t="b">
-        <v>1</v>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2027-01-04T18:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -3808,8 +3656,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dresden-das-kalte-haus-im-schnellcheck-a-849bf1d3-1f83-42d8-be48-d357771a477c</t>
         </is>
       </c>
-      <c r="G112" t="b">
-        <v>1</v>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2026-05-20T20:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -3839,8 +3689,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dresden-das-kalte-haus-im-schnellcheck-a-4f4642d0-88cc-4081-8f80-e394e54149fe</t>
         </is>
       </c>
-      <c r="G113" t="b">
-        <v>1</v>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2026-05-20T20:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -3870,9 +3722,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-berlin-das-leben-nach-dem-tod-im-schnellcheck-a-1294583.html</t>
         </is>
       </c>
-      <c r="G114" t="b">
-        <v>0</v>
-      </c>
+      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3901,8 +3751,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-berlin-das-maedchen-das-allein-nach-haus-geht-im-schnellcheck-a-38dcc3ad-f2a0-4981-b511-3129581ee5b6</t>
         </is>
       </c>
-      <c r="G115" t="b">
-        <v>1</v>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2027-01-05T22:59:59Z</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -3932,8 +3784,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-hessen-das-monster-von-kassel-im-schnellcheck-a-1266025.html</t>
         </is>
       </c>
-      <c r="G116" t="b">
-        <v>1</v>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2026-08-26T21:59:00Z</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -3963,8 +3817,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dresden-das-nest-im-schnellcheck-a-1263831.html</t>
         </is>
       </c>
-      <c r="G117" t="b">
-        <v>1</v>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2026-10-01T20:10:00Z</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -3994,8 +3850,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dresden-das-nest-im-schnellcheck-a-0decf517-b93e-4168-b392-cba85dd9b1f7</t>
         </is>
       </c>
-      <c r="G118" t="b">
-        <v>1</v>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2026-10-01T20:10:00Z</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -4025,8 +3883,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-berlin-mit-mark-waschke-das-opfer-im-schnellcheck-a-aa72726d-662c-451d-8b42-ba93c4fa42b6</t>
         </is>
       </c>
-      <c r="G119" t="b">
-        <v>1</v>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2026-06-30T21:59:00Z</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -4056,8 +3916,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-berlin-das-perfekte-verbrechen-im-schnellcheck-a-f35c9585-158a-4b3f-b724-499c12ba4156</t>
         </is>
       </c>
-      <c r="G120" t="b">
-        <v>1</v>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2026-06-23T21:59:59Z</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -4087,9 +3949,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-franken-der-schnellcheck-a-1091599.html</t>
         </is>
       </c>
-      <c r="G121" t="b">
-        <v>0</v>
-      </c>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4118,9 +3978,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dortmund-das-team-im-schnellcheck-a-1300207.html</t>
         </is>
       </c>
-      <c r="G122" t="b">
-        <v>0</v>
-      </c>
+      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4149,9 +4007,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-wien-das-tor-zur-hoelle-im-schnellcheck-a-893f1a1d-7a43-428b-96be-243b82175272</t>
         </is>
       </c>
-      <c r="G123" t="b">
-        <v>0</v>
-      </c>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4180,9 +4036,7 @@
           <t>https://www.spiegel.de/kultur/tatort-heute-aus-ludwigshafen-das-verhoer-mit-goetz-otto-im-schnellcheck-a-f9c96c7e-4da1-40cd-b93c-672c4f3ee87e</t>
         </is>
       </c>
-      <c r="G124" t="b">
-        <v>0</v>
-      </c>
+      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4211,8 +4065,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenchen-das-verlangen-mit-batic-und-leitmayr-im-schnellcheck-a-ec73aa38-8cdb-4581-a156-0a37d46838fb</t>
         </is>
       </c>
-      <c r="G125" t="b">
-        <v>1</v>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2026-12-26T16:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -4242,9 +4098,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-goettingen-das-verschwundene-kind-im-schnellcheck-a-1248742.html</t>
         </is>
       </c>
-      <c r="G126" t="b">
-        <v>0</v>
-      </c>
+      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4273,8 +4127,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenchen-das-wunderkind-im-schnellcheck-a-01f541d5-0e53-4833-8435-9c839828a6e2</t>
         </is>
       </c>
-      <c r="G127" t="b">
-        <v>1</v>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2026-11-18T20:45:00Z</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -4300,8 +4156,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-lena-odenthal-dein-gutes-recht-im-schnellcheck-a-def58834-a26a-4f87-8e89-f7e6861f00c6</t>
         </is>
       </c>
-      <c r="G128" t="b">
-        <v>1</v>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2026-04-14T20:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -4331,9 +4189,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-berlin-dein-name-sei-harbinger-im-schnellcheck-a-2e4151b9-eee1-4375-ac6e-69523b1732ff</t>
         </is>
       </c>
-      <c r="G129" t="b">
-        <v>0</v>
-      </c>
+      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4362,9 +4218,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-berlin-dein-name-sei-harbinger-im-schnellcheck-a-1181047.html</t>
         </is>
       </c>
-      <c r="G130" t="b">
-        <v>0</v>
-      </c>
+      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4393,9 +4247,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-wien-dein-verlust-mit-eisner-und-fellner-im-schnellcheck-a-b132e4d1-cd16-420e-b2d4-b93defdf78f1</t>
         </is>
       </c>
-      <c r="G131" t="b">
-        <v>0</v>
-      </c>
+      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4424,9 +4276,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-wien-deine-mutter-im-schnellcheck-a-faab71dc-00ea-445f-8462-e42fb48374f0</t>
         </is>
       </c>
-      <c r="G132" t="b">
-        <v>0</v>
-      </c>
+      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4455,8 +4305,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dresden-deja-vu-im-schnellcheck-a-1189907.html</t>
         </is>
       </c>
-      <c r="G133" t="b">
-        <v>1</v>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>2026-05-16T20:20:00Z</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -4486,8 +4338,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-ludwigshafen-der-boese-koenig-im-schnellcheck-a-bf942c9c-75f6-4d13-9209-fd28819c7537</t>
         </is>
       </c>
-      <c r="G134" t="b">
-        <v>1</v>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2026-05-14T20:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -4517,9 +4371,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-der-schweiz-der-elefant-im-raum-im-schnellcheck-a-1293096.html</t>
         </is>
       </c>
-      <c r="G135" t="b">
-        <v>0</v>
-      </c>
+      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4548,9 +4400,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-wien-der-elektriker-im-schnellcheck-a-63417778-0769-48a4-a702-ef3296add378</t>
         </is>
       </c>
-      <c r="G136" t="b">
-        <v>0</v>
-      </c>
+      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4575,9 +4425,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-charlotte-lindholm-der-fall-holdt-im-schnellcheck-a-1175670.html</t>
         </is>
       </c>
-      <c r="G137" t="b">
-        <v>0</v>
-      </c>
+      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4606,9 +4454,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-kiel-der-fluch-der-weissen-moewe-im-schnellcheck-a-4b903aed-0220-4bef-b9a4-ece7279cd344</t>
         </is>
       </c>
-      <c r="G138" t="b">
-        <v>0</v>
-      </c>
+      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4637,8 +4483,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-saarbruecken-der-fluch-des-geldes-im-schnellcheck-a-f403a3d1-c6c5-4501-8d56-84664dbf74d7</t>
         </is>
       </c>
-      <c r="G139" t="b">
-        <v>1</v>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2027-01-05T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -4668,9 +4516,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-berlin-der-gute-weg-im-schnellcheck-a-1265468.html</t>
         </is>
       </c>
-      <c r="G140" t="b">
-        <v>0</v>
-      </c>
+      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4699,8 +4545,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-saarbruecken-der-herr-des-waldes-im-schnellcheck-a-3212fa93-e7dd-4572-a25b-863727356c66</t>
         </is>
       </c>
-      <c r="G141" t="b">
-        <v>1</v>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2027-01-19T22:59:00Z</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -4730,8 +4578,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-weimar-der-hoellische-heinz-a-1242359.html</t>
         </is>
       </c>
-      <c r="G142" t="b">
-        <v>1</v>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2026-04-07T19:44:00Z</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -4761,8 +4611,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-bremen-der-hundertste-affe-im-schnellcheck-a-1089361.html</t>
         </is>
       </c>
-      <c r="G143" t="b">
-        <v>1</v>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>2026-05-17T22:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="144">
@@ -4792,8 +4644,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-aus-weimar-der-kalte-fritte-im-schnellcheck-a-1192081.html</t>
         </is>
       </c>
-      <c r="G144" t="b">
-        <v>1</v>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2026-09-03T20:10:00Z</t>
+        </is>
       </c>
     </row>
     <row r="145">
@@ -4823,8 +4677,10 @@
           <t>https://www.spiegel.de/kultur/tv/wunsch-tatort-heute-aus-weimar-der-kalte-fritte-im-schnellcheck-a-4676cd12-b8bc-4499-a2b8-e6c351388d2b</t>
         </is>
       </c>
-      <c r="G145" t="b">
-        <v>1</v>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>2026-09-03T20:10:00Z</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -4854,8 +4710,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dresden-der-koenig-der-gosse-im-schnellcheck-a-1114345.html</t>
         </is>
       </c>
-      <c r="G146" t="b">
-        <v>1</v>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>2026-07-23T20:10:00Z</t>
+        </is>
       </c>
     </row>
     <row r="147">
@@ -4885,9 +4743,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-weimar-der-letzte-schrey-im-schnellcheck-a-f9d1101c-ee3e-4e34-8600-945f9441cc59</t>
         </is>
       </c>
-      <c r="G147" t="b">
-        <v>0</v>
-      </c>
+      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4916,9 +4772,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenster-der-mann-der-in-den-dschungel-fiel-im-schnellcheck-a-7e71c0d2-b38b-4885-9e6b-385cb0bc6085</t>
         </is>
       </c>
-      <c r="G148" t="b">
-        <v>0</v>
-      </c>
+      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4947,9 +4801,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-stuttgart-der-mann-der-luegt-im-schnellcheck-a-1234737.html</t>
         </is>
       </c>
-      <c r="G149" t="b">
-        <v>0</v>
-      </c>
+      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4978,9 +4830,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-stuttgart-der-moerder-in-mir-im-schnellcheck-a-9b10a33f-f4d2-49fe-b5f2-4972b2fe3abd</t>
         </is>
       </c>
-      <c r="G150" t="b">
-        <v>0</v>
-      </c>
+      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5009,9 +4859,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-saarbruecken-der-pakt-im-schnellcheck-a-1248090.html</t>
         </is>
       </c>
-      <c r="G151" t="b">
-        <v>0</v>
-      </c>
+      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5040,8 +4888,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dem-schwarzwald-der-reini-im-schnellcheck-a-23238bde-cd9b-44a3-b46e-2a2f117de56f</t>
         </is>
       </c>
-      <c r="G152" t="b">
-        <v>1</v>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>2026-11-16T18:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="153">
@@ -5071,8 +4921,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-der-reiz-des-boesen-im-schnellcheck-a-2066f915-c9e7-44d9-886f-8a4fb55e457a</t>
         </is>
       </c>
-      <c r="G153" t="b">
-        <v>1</v>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>2026-11-25T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="154">
@@ -5102,9 +4954,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-weimar-der-scheidende-schupo-mit-christian-ulmen-im-schnellcheck-a-1132080.html</t>
         </is>
       </c>
-      <c r="G154" t="b">
-        <v>0</v>
-      </c>
+      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5133,9 +4983,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-aus-ludwigshafen-der-stelzenmann-im-schnellcheck-a-1caf22cc-0ceb-4718-8125-58bcaedd4d90</t>
         </is>
       </c>
-      <c r="G155" t="b">
-        <v>0</v>
-      </c>
+      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5164,9 +5012,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-der-tod-der-anderen-im-schnellcheck-a-8a706b1e-df63-4c35-8226-ce703b394a41</t>
         </is>
       </c>
-      <c r="G156" t="b">
-        <v>0</v>
-      </c>
+      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5195,8 +5041,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenchen-der-tod-ist-unser-ganzes-leben-im-schnellcheck-a-1143580.html</t>
         </is>
       </c>
-      <c r="G157" t="b">
-        <v>1</v>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>2026-09-24T21:30:00Z</t>
+        </is>
       </c>
     </row>
     <row r="158">
@@ -5226,8 +5074,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-weimar-mit-ulmen-und-tschirner-der-schnellcheck-a-1088524.html</t>
         </is>
       </c>
-      <c r="G158" t="b">
-        <v>1</v>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2026-02-19T21:10:00Z</t>
+        </is>
       </c>
     </row>
     <row r="159">
@@ -5257,8 +5107,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-frankfurt-der-turm-im-schnellcheck-a-1241894.html</t>
         </is>
       </c>
-      <c r="G159" t="b">
-        <v>1</v>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>2026-03-19T20:59:00Z</t>
+        </is>
       </c>
     </row>
     <row r="160">
@@ -5288,9 +5140,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-stuttgart-der-videobeweis-im-schnellcheck-a-b580ccf5-be40-4286-9a3e-de1e8596905a</t>
         </is>
       </c>
-      <c r="G160" t="b">
-        <v>0</v>
-      </c>
+      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5319,9 +5169,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-stuttgart-der-welten-lohn-im-schnellcheck-a-662d7285-cb6c-43e7-9edf-21136314e1ac</t>
         </is>
       </c>
-      <c r="G161" t="b">
-        <v>0</v>
-      </c>
+      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5350,9 +5198,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-stuttgart-der-welten-lohn-im-schnellcheck-a-b154b03d-5e17-49b1-a311-f8a2d296e25a</t>
         </is>
       </c>
-      <c r="G162" t="b">
-        <v>0</v>
-      </c>
+      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5381,8 +5227,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-weimar-der-wueste-gobi-im-schnellcheck-a-1182557.html</t>
         </is>
       </c>
-      <c r="G163" t="b">
-        <v>1</v>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>2026-04-15T20:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="164">
@@ -5412,9 +5260,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-des-anderen-last-im-schnellcheck-a-61fbe155-2c3d-4461-8136-134ca9b26906</t>
         </is>
       </c>
-      <c r="G164" t="b">
-        <v>0</v>
-      </c>
+      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5443,8 +5289,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenster-des-teufels-langer-atem-im-schnellcheck-a-32baa06b-0819-485c-8a2b-fa7ad222b205</t>
         </is>
       </c>
-      <c r="G165" t="b">
-        <v>1</v>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>2026-12-29T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="166">
@@ -5474,9 +5322,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-aus-wien-die-amme-im-schnellcheck-a-162e369e-187e-4952-9583-034755dd9515</t>
         </is>
       </c>
-      <c r="G166" t="b">
-        <v>0</v>
-      </c>
+      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5505,8 +5351,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dem-schwarzwald-die-blicke-der-anderen-im-schnellcheck-a-abe28a92-d0f1-4722-8415-fcaa9bc78e44</t>
         </is>
       </c>
-      <c r="G167" t="b">
-        <v>1</v>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>2026-12-02T21:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="168">
@@ -5536,8 +5384,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-berlin-die-dritte-haut-im-schnellcheck-a-af06000c-8748-4790-bb70-f46f5c1d4026</t>
         </is>
       </c>
-      <c r="G168" t="b">
-        <v>1</v>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>2026-12-01T22:59:59Z</t>
+        </is>
       </c>
     </row>
     <row r="169">
@@ -5567,8 +5417,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenster-die-erfindung-des-rades-im-schnellcheck-a-1ac787dc-aa68-4b78-afcc-38acaed87897</t>
         </is>
       </c>
-      <c r="G169" t="b">
-        <v>1</v>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>2026-12-07T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="170">
@@ -5598,9 +5450,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenchen-die-ewige-welle-im-schnellcheck-a-1268591.html</t>
         </is>
       </c>
-      <c r="G170" t="b">
-        <v>0</v>
-      </c>
+      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5629,9 +5479,7 @@
           <t>https://www.spiegel.de/kultur/tv/wunsch-tatort-heute-aus-wien-die-faust-im-schnellcheck-a-c063f71a-0564-416f-859b-81135ba7a55c</t>
         </is>
       </c>
-      <c r="G171" t="b">
-        <v>0</v>
-      </c>
+      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5660,9 +5508,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-wien-die-faust-im-schnellcheck-a-1187248.html</t>
         </is>
       </c>
-      <c r="G172" t="b">
-        <v>0</v>
-      </c>
+      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5691,9 +5537,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-frankfurt-der-psycho-krimi-im-schnellcheck-a-1086243.html</t>
         </is>
       </c>
-      <c r="G173" t="b">
-        <v>0</v>
-      </c>
+      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5718,8 +5562,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-wotan-wilke-moehring-die-goldene-zeit-im-schnellcheck-a-0dbbe256-c575-4270-8c38-a570a6f04027</t>
         </is>
       </c>
-      <c r="G174" t="b">
-        <v>1</v>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>2026-09-17T20:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="175">
@@ -5745,8 +5591,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-wotan-wilke-moehring-die-goldene-zeit-im-schnellcheck-a-dde177ce-20b2-491f-bec7-d7dbcb2ff819</t>
         </is>
       </c>
-      <c r="G175" t="b">
-        <v>1</v>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>2026-09-17T20:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="176">
@@ -5772,8 +5620,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-wotan-wilke-moehring-die-goldene-zeit-im-schnellcheck-a-332c814e-1912-4159-abd8-cd5cadee898b</t>
         </is>
       </c>
-      <c r="G176" t="b">
-        <v>1</v>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>2026-09-17T20:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="177">
@@ -5803,9 +5653,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dem-schwarzwald-die-grosse-angst-im-schnellcheck-a-a91ffed4-8db6-46a5-a3e9-dac60a62f779</t>
         </is>
       </c>
-      <c r="G177" t="b">
-        <v>0</v>
-      </c>
+      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5834,9 +5682,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-frankfurt-die-guten-und-die-boesen-im-schnellcheck-a-df1cf05c-bd3b-463b-804a-6d1bea19db19</t>
         </is>
       </c>
-      <c r="G178" t="b">
-        <v>0</v>
-      </c>
+      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5865,9 +5711,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-weimar-die-harte-kern-im-schnellcheck-a-1287320.html</t>
         </is>
       </c>
-      <c r="G179" t="b">
-        <v>0</v>
-      </c>
+      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5896,8 +5740,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-saarbruecken-der-ard-sonntagskrimi-im-schnellcheck-a-e481e713-ae7e-4f63-a911-d5b8d3c31abf</t>
         </is>
       </c>
-      <c r="G180" t="b">
-        <v>1</v>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>2027-01-14T22:29:00Z</t>
+        </is>
       </c>
     </row>
     <row r="181">
@@ -5927,9 +5773,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-berlin-die-kalten-und-die-toten-im-schnellcheck-a-71e5eecc-93ee-4753-b18c-80db5df41626</t>
         </is>
       </c>
-      <c r="G181" t="b">
-        <v>0</v>
-      </c>
+      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5958,8 +5802,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-wien-die-kunst-des-krieges-im-schnellcheck-a-345643d4-2fef-4db7-9ef2-a9e1607530a8</t>
         </is>
       </c>
-      <c r="G182" t="b">
-        <v>0</v>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>2026-01-27T22:59:00Z</t>
+        </is>
       </c>
     </row>
     <row r="183">
@@ -5989,8 +5835,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-wien-die-kunst-des-krieges-im-schnellcheck-a-1103118.html</t>
         </is>
       </c>
-      <c r="G183" t="b">
-        <v>0</v>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>2026-01-27T22:59:00Z</t>
+        </is>
       </c>
     </row>
     <row r="184">
@@ -6016,9 +5864,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-wotan-wilke-moehring-die-macht-der-familie-im-schnellcheck-a-409d179b-9493-4f33-846d-547c405b32d2</t>
         </is>
       </c>
-      <c r="G184" t="b">
-        <v>0</v>
-      </c>
+      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6047,9 +5893,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-der-schweiz-die-musik-stirbt-zuletzt-im-schnellcheck-a-1220983.html</t>
         </is>
       </c>
-      <c r="G185" t="b">
-        <v>0</v>
-      </c>
+      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6078,9 +5922,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-stuttgart-die-nacht-der-kommissare-im-schnellcheck-a-dd02abc0-4f54-46c8-84a9-e3d2a9154e21</t>
         </is>
       </c>
-      <c r="G186" t="b">
-        <v>0</v>
-      </c>
+      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6109,9 +5951,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-franken-die-nacht-gehoert-dir-im-schnellcheck-a-ee809754-7a7f-442c-91b1-0f28f31cb985</t>
         </is>
       </c>
-      <c r="G187" t="b">
-        <v>0</v>
-      </c>
+      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6136,9 +5976,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-odenthal-die-pfalz-von-oben-im-schnellcheck-a-1295778.html</t>
         </is>
       </c>
-      <c r="G188" t="b">
-        <v>0</v>
-      </c>
+      <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6167,8 +6005,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-goettingen-die-rache-an-der-welt-im-schnellcheck-a-01c2109f-b751-40b8-8e27-6a43aab2f206</t>
         </is>
       </c>
-      <c r="G189" t="b">
-        <v>1</v>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>2026-10-21T20:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="190">
@@ -6198,8 +6038,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-weimar-die-robuste-roswita-im-schnellcheck-a-1224201.html</t>
         </is>
       </c>
-      <c r="G190" t="b">
-        <v>1</v>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>2026-09-24T20:10:00Z</t>
+        </is>
       </c>
     </row>
     <row r="191">
@@ -6229,8 +6071,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-die-schoepfung-im-schnellcheck-a-26b6725d-1b63-4b21-801d-fbc87f933982</t>
         </is>
       </c>
-      <c r="G191" t="b">
-        <v>1</v>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>2027-01-11T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="192">
@@ -6256,8 +6100,10 @@
           <t>https://www.spiegel.de/kultur/tv/muenchen-tatort-heute-die-wahrheit-im-schnellcheck-a-5c3e02ee-cb94-4317-8f35-b77c73a1b7a0</t>
         </is>
       </c>
-      <c r="G192" t="b">
-        <v>1</v>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2026-09-23T21:30:00Z</t>
+        </is>
       </c>
     </row>
     <row r="193">
@@ -6287,8 +6133,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenchen-die-wahrheit-im-schnellcheck-a-1116455.html</t>
         </is>
       </c>
-      <c r="G193" t="b">
-        <v>1</v>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>2026-09-23T21:30:00Z</t>
+        </is>
       </c>
     </row>
     <row r="194">
@@ -6318,8 +6166,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dresden-die-zeit-ist-gekommen-im-schnellcheck-a-0f88c071-df9e-4dd4-9e7f-8922efb8a745</t>
         </is>
       </c>
-      <c r="G194" t="b">
-        <v>1</v>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>2026-08-20T20:10:00Z</t>
+        </is>
       </c>
     </row>
     <row r="195">
@@ -6349,9 +6199,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-aus-magdeburg-hexen-brennen-im-schnellcheck-a-df9d65aa-fc04-4720-85ff-4ad91b46a3b0</t>
         </is>
       </c>
-      <c r="G195" t="b">
-        <v>0</v>
-      </c>
+      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6380,8 +6228,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-diesmal-ist-es-anders-im-schnellcheck-a-ce6b5398-347b-42da-a276-aa7c01b9039f</t>
         </is>
       </c>
-      <c r="G196" t="b">
-        <v>1</v>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>2026-05-10T18:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="197">
@@ -6411,8 +6261,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-bremen-donuts-im-schnellcheck-a-781bedf0-9602-42b7-96cb-a6967061d82f</t>
         </is>
       </c>
-      <c r="G197" t="b">
-        <v>1</v>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>2026-11-18T21:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="198">
@@ -6442,8 +6294,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenchen-dreams-im-schnellcheck-a-6fef14d3-c3c7-484e-ba8a-ad3c660d9c3e</t>
         </is>
       </c>
-      <c r="G198" t="b">
-        <v>1</v>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>2026-07-15T20:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="199">
@@ -6473,9 +6327,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-stuttgart-du-allein-im-schnellcheck-a-38a7aa8e-2482-4212-997f-aeb462e8c858</t>
         </is>
       </c>
-      <c r="G199" t="b">
-        <v>0</v>
-      </c>
+      <c r="G199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6504,9 +6356,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dortmund-du-bleibst-hier-im-schnellcheck-a-85cc1deb-6d99-4356-9133-fbe0d7c729d9</t>
         </is>
       </c>
-      <c r="G200" t="b">
-        <v>0</v>
-      </c>
+      <c r="G200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6535,9 +6385,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-ludwigshafen-du-gehoerst-mir-der-check-a-1074285.html</t>
         </is>
       </c>
-      <c r="G201" t="b">
-        <v>0</v>
-      </c>
+      <c r="G201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6562,9 +6410,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-berlin-dunkelfeld-mit-mark-waschke-im-schnellcheck-a-1124614.html</t>
         </is>
       </c>
-      <c r="G202" t="b">
-        <v>0</v>
-      </c>
+      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6593,8 +6439,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-frankfurt-dunkelheit-im-schnellcheck-a-5f5d6b7d-eaba-433c-a48c-6ed9e7687181</t>
         </is>
       </c>
-      <c r="G203" t="b">
-        <v>1</v>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>2026-10-05T21:59:00Z</t>
+        </is>
       </c>
     </row>
     <row r="204">
@@ -6624,9 +6472,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-aus-rostock-dunkler-zwilling-im-schnellcheck-a-1288197.html</t>
         </is>
       </c>
-      <c r="G204" t="b">
-        <v>0</v>
-      </c>
+      <c r="G204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6655,9 +6501,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-durchgedreht-im-schnellcheck-a-1104653.html</t>
         </is>
       </c>
-      <c r="G205" t="b">
-        <v>0</v>
-      </c>
+      <c r="G205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -6686,8 +6530,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-bremen-echolot-im-schnellcheck-a-1115882.html</t>
         </is>
       </c>
-      <c r="G206" t="b">
-        <v>1</v>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>2026-06-23T20:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="207">
@@ -6717,8 +6563,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenster-ein-freund-ein-guter-freund-im-schnellcheck-a-2d123eed-3e61-4aeb-811a-f8a6fa55535f</t>
         </is>
       </c>
-      <c r="G207" t="b">
-        <v>1</v>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>2026-06-18T18:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="208">
@@ -6748,8 +6596,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenster-ein-fuss-kommt-selten-alleine-schnellcheck-a-1089363.html</t>
         </is>
       </c>
-      <c r="G208" t="b">
-        <v>1</v>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>2026-12-22T21:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="209">
@@ -6775,9 +6625,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-wotan-wilke-moehring-schwarzer-schnee-im-schnellcheck-a-4b034f38-290d-4a1a-adcd-9bb963bfb03e</t>
         </is>
       </c>
-      <c r="G209" t="b">
-        <v>0</v>
-      </c>
+      <c r="G209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -6806,8 +6654,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-berlin-schnellcheck-zu-ein-paar-worte-nach-mitternacht-a-63b5b07c-1f90-49b8-b764-32c6c37f0668</t>
         </is>
       </c>
-      <c r="G210" t="b">
-        <v>1</v>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>2026-12-29T22:59:00Z</t>
+        </is>
       </c>
     </row>
     <row r="211">
@@ -6837,9 +6687,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-franken-ein-tag-wie-jeder-andere-im-schnellcheck-a-1254099.html</t>
         </is>
       </c>
-      <c r="G211" t="b">
-        <v>0</v>
-      </c>
+      <c r="G211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -6868,8 +6716,10 @@
           <t>https://www.spiegel.de/kultur/tatort-heute-aus-hessen-erbarmen-zu-spaet-im-schnellcheck-a-223c6d46-23d2-447f-ac80-63548dac97a0</t>
         </is>
       </c>
-      <c r="G212" t="b">
-        <v>1</v>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>2026-11-10T21:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="213">
@@ -6899,8 +6749,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-berlin-erika-mustermann-im-schnellcheck-a-2c001506-3567-4e6f-9872-57a5dddfc190</t>
         </is>
       </c>
-      <c r="G213" t="b">
-        <v>1</v>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>2026-11-02T19:14:00Z</t>
+        </is>
       </c>
     </row>
     <row r="214">
@@ -6930,9 +6782,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-frankfurt-es-gruent-so-gruen-wenn-frankfurts-berge-bluehn-a-6dba3998-ca6f-4ada-86e3-c055b80db842</t>
         </is>
       </c>
-      <c r="G214" t="b">
-        <v>0</v>
-      </c>
+      <c r="G214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -6957,9 +6807,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-ulrich-tukur-als-murot-der-schnellcheck-a-1119253.html</t>
         </is>
       </c>
-      <c r="G215" t="b">
-        <v>0</v>
-      </c>
+      <c r="G215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -6988,9 +6836,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-zuerich-faehrmann-im-schnellcheck-a-15fd2b57-af8d-422a-b7b0-75b0ac6e4abf</t>
         </is>
       </c>
-      <c r="G216" t="b">
-        <v>0</v>
-      </c>
+      <c r="G216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7019,9 +6865,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-frankfurt-falscher-hase-im-schnellcheck-a-1282018.html</t>
         </is>
       </c>
-      <c r="G217" t="b">
-        <v>0</v>
-      </c>
+      <c r="G217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7050,8 +6894,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-familien-im-schnellcheck-a-1204490.html</t>
         </is>
       </c>
-      <c r="G218" t="b">
-        <v>1</v>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>2026-07-06T18:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="219">
@@ -7081,8 +6927,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenster-fangschuss-mit-boerne-und-thiel-im-schnellcheck-a-1139887.html</t>
         </is>
       </c>
-      <c r="G219" t="b">
-        <v>1</v>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>2026-06-19T19:45:00Z</t>
+        </is>
       </c>
     </row>
     <row r="220">
@@ -7112,8 +6960,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenster-fangschuss-mit-boerne-und-thiel-im-schnellcheck-a-d2b7ade1-ad0b-4ed7-bd20-7c8e2a836c11</t>
         </is>
       </c>
-      <c r="G220" t="b">
-        <v>1</v>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>2026-06-19T19:45:00Z</t>
+        </is>
       </c>
     </row>
     <row r="221">
@@ -7143,8 +6993,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenster-feierstunde-mit-boerne-und-thiel-im-schnellcheck-a-1113084.html</t>
         </is>
       </c>
-      <c r="G221" t="b">
-        <v>1</v>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>2026-06-03T18:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="222">
@@ -7174,8 +7026,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dortmund-feuer-im-schnellcheck-a-cadb9a25-e0e5-4e41-93a4-98f68092d081</t>
         </is>
       </c>
-      <c r="G222" t="b">
-        <v>1</v>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>2026-06-09T18:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="223">
@@ -7205,8 +7059,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenster-fiderallala-mit-boerne-und-thiel-im-schnellcheck-a-22ac53d4-2412-4494-acbb-26817263e22d</t>
         </is>
       </c>
-      <c r="G223" t="b">
-        <v>1</v>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>2026-07-06T19:45:00Z</t>
+        </is>
       </c>
     </row>
     <row r="224">
@@ -7236,8 +7092,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-frankfurt-finsternis-im-schnellcheck-a-cd398fbd-2de7-43fd-98d4-ba8691f87f7e</t>
         </is>
       </c>
-      <c r="G224" t="b">
-        <v>1</v>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>2027-02-16T22:59:00Z</t>
+        </is>
       </c>
     </row>
     <row r="225">
@@ -7267,8 +7125,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenchen-schnellcheck-zu-flash-a-374421a7-519f-488a-8df4-6cad22bf6d21</t>
         </is>
       </c>
-      <c r="G225" t="b">
-        <v>1</v>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:30:00Z</t>
+        </is>
       </c>
     </row>
     <row r="226">
@@ -7298,9 +7158,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenchen-freies-land-im-schnellcheck-a-1209478.html</t>
         </is>
       </c>
-      <c r="G226" t="b">
-        <v>0</v>
-      </c>
+      <c r="G226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7329,9 +7187,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-der-schweiz-freitod-mit-reto-flueckiger-schnellcheck-a-1112262.html</t>
         </is>
       </c>
-      <c r="G227" t="b">
-        <v>0</v>
-      </c>
+      <c r="G227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7360,9 +7216,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-der-schweiz-friss-oder-stirb-im-schnellcheck-a-1244607.html</t>
         </is>
       </c>
-      <c r="G228" t="b">
-        <v>0</v>
-      </c>
+      <c r="G228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7387,8 +7241,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heike-makatsch-als-kommissarin-in-freiburg-schnellcheck-a-1083972.html</t>
         </is>
       </c>
-      <c r="G229" t="b">
-        <v>1</v>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>2026-07-12T21:59:00Z</t>
+        </is>
       </c>
     </row>
     <row r="230">
@@ -7418,9 +7274,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-frankfurt-funkstille-im-schnellcheck-a-2d1e57e5-3168-4588-aba7-39632b7a0967</t>
         </is>
       </c>
-      <c r="G230" t="b">
-        <v>0</v>
-      </c>
+      <c r="G230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7449,9 +7303,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dem-schwarzwald-fuer-immer-und-dich-im-schnellcheck-a-1254302.html</t>
         </is>
       </c>
-      <c r="G231" t="b">
-        <v>0</v>
-      </c>
+      <c r="G231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7480,9 +7332,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-frankfurt-fuerchte-dich-im-schnellcheck-a-1172932.html</t>
         </is>
       </c>
-      <c r="G232" t="b">
-        <v>0</v>
-      </c>
+      <c r="G232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7511,9 +7361,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenchen-game-over-im-schnellcheck-a-64e1cacb-7912-4f76-933e-f73c57447066</t>
         </is>
       </c>
-      <c r="G233" t="b">
-        <v>0</v>
-      </c>
+      <c r="G233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7542,9 +7390,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-gefangen-im-schnellcheck-a-75390e49-e7da-454c-87cb-1bee57d02767</t>
         </is>
       </c>
-      <c r="G234" t="b">
-        <v>0</v>
-      </c>
+      <c r="G234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7573,9 +7419,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-gefangen-im-schnellcheck-a-940813c5-cc5c-4c11-ac6f-a1c57e2e0c62</t>
         </is>
       </c>
-      <c r="G235" t="b">
-        <v>0</v>
-      </c>
+      <c r="G235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -7604,8 +7448,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-goettingen-geisterfahrt-im-schnellcheck-a-abde6c38-0594-4ad6-b4ea-a929c7c270d0</t>
         </is>
       </c>
-      <c r="G236" t="b">
-        <v>1</v>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>2026-02-23T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="237">
@@ -7635,9 +7481,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dortmund-gier-und-angst-im-schnellcheck-a-de32b64b-e98d-4370-92ec-00a5e2e9dafa</t>
         </is>
       </c>
-      <c r="G237" t="b">
-        <v>0</v>
-      </c>
+      <c r="G237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -7666,9 +7510,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-wien-glueck-allein-im-schnellcheck-a-1269599.html</t>
         </is>
       </c>
-      <c r="G238" t="b">
-        <v>0</v>
-      </c>
+      <c r="G238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -7697,9 +7539,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-ludwigshafen-mit-lena-odenthal-gold-im-schnellcheck-a-4559d3f1-6613-4410-ba71-e6c8f73ee8dc</t>
         </is>
       </c>
-      <c r="G239" t="b">
-        <v>0</v>
-      </c>
+      <c r="G239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -7728,9 +7568,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dem-schwarzwald-goldbach-im-schnellcheck-a-1169982.html</t>
         </is>
       </c>
-      <c r="G240" t="b">
-        <v>0</v>
-      </c>
+      <c r="G240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -7759,8 +7597,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-aus-muenster-gott-ist-auch-nur-ein-mensch-im-schnellcheck-a-1177977.html</t>
         </is>
       </c>
-      <c r="G241" t="b">
-        <v>1</v>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>2026-08-19T18:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="242">
@@ -7790,9 +7630,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenchen-hackl-im-schnellcheck-a-b6377686-9907-4f94-96fc-a7a7e92355f7</t>
         </is>
       </c>
-      <c r="G242" t="b">
-        <v>0</v>
-      </c>
+      <c r="G242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -7821,9 +7659,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-stuttgart-hal-mit-ken-duken-im-schnellcheck-a-1103582.html</t>
         </is>
       </c>
-      <c r="G243" t="b">
-        <v>0</v>
-      </c>
+      <c r="G243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -7852,9 +7688,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-aus-muenchen-hardcore-ueber-pornoproduzenten-a-1170998.html</t>
         </is>
       </c>
-      <c r="G244" t="b">
-        <v>0</v>
-      </c>
+      <c r="G244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -7883,9 +7717,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dortmund-heile-welt-im-schnellcheck-a-d330c6ee-26c4-456c-bfd7-f71ea94b07f4</t>
         </is>
       </c>
-      <c r="G245" t="b">
-        <v>0</v>
-      </c>
+      <c r="G245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -7914,9 +7746,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dortmund-heile-welt-im-schnellcheck-a-2e1bb6aa-b52c-4cd5-aa27-a55c979f5250</t>
         </is>
       </c>
-      <c r="G246" t="b">
-        <v>0</v>
-      </c>
+      <c r="G246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -7945,9 +7775,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-wien-her-mit-der-marie-im-schnellcheck-a-1229482.html</t>
         </is>
       </c>
-      <c r="G247" t="b">
-        <v>0</v>
-      </c>
+      <c r="G247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -7976,8 +7804,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dresden-herz-der-dunkelheit-im-schnellcheck-a-03310c99-378b-463f-a2e5-2d627970a184</t>
         </is>
       </c>
-      <c r="G248" t="b">
-        <v>1</v>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>2026-02-02T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="249">
@@ -8007,9 +7837,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-ludwigshafen-hetzjagd-im-schnellcheck-a-15f27d7f-87c4-4d09-b2d4-487bb4dd2e54</t>
         </is>
       </c>
-      <c r="G249" t="b">
-        <v>0</v>
-      </c>
+      <c r="G249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8034,8 +7862,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-fabian-hinrichs-hochamt-fuer-toni-im-schnellcheck-a-103b5c0e-0d93-440e-94a7-86d0926c5d82</t>
         </is>
       </c>
-      <c r="G250" t="b">
-        <v>1</v>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>2026-08-24T17:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="251">
@@ -8065,8 +7895,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-hubertys-rache-im-schnellcheck-a-9690ea2b-c662-4ff2-abba-12c1b0339bc7</t>
         </is>
       </c>
-      <c r="G251" t="b">
-        <v>1</v>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>2026-10-28T21:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="252">
@@ -8092,8 +7924,10 @@
           <t>https://www.spiegel.de/kultur/tv/dortmund-tatort-hundstage-mit-joerg-hartmann-anna-schudt-der-check-a-1071682.html</t>
         </is>
       </c>
-      <c r="G252" t="b">
-        <v>1</v>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>2026-12-16T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="253">
@@ -8123,9 +7957,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-stuttgart-hueter-der-schwelle-im-schnellcheck-a-1287750.html</t>
         </is>
       </c>
-      <c r="G253" t="b">
-        <v>0</v>
-      </c>
+      <c r="G253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -8154,9 +7986,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dem-schwarzwald-masken-im-schnellcheck-a-23aaa54c-07f1-4436-b734-22187ee92fdf</t>
         </is>
       </c>
-      <c r="G254" t="b">
-        <v>0</v>
-      </c>
+      <c r="G254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -8185,9 +8015,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-franken-ich-seh-dich-mit-fabian-hinrichs-im-schnellcheck-a-2343a88a-8c5d-4f6b-a839-6a2a5a1eb5cf</t>
         </is>
       </c>
-      <c r="G255" t="b">
-        <v>0</v>
-      </c>
+      <c r="G255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -8216,9 +8044,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-franken-ich-toete-niemand-im-schnellcheck-a-1201653.html</t>
         </is>
       </c>
-      <c r="G256" t="b">
-        <v>0</v>
-      </c>
+      <c r="G256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -8247,9 +8073,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-stuttgart-im-gelobten-land-lohnt-sich-das-einschalten-a-1074501.html</t>
         </is>
       </c>
-      <c r="G257" t="b">
-        <v>0</v>
-      </c>
+      <c r="G257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -8278,9 +8102,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-bremen-im-toten-winkel-im-schnellcheck-a-1196864.html</t>
         </is>
       </c>
-      <c r="G258" t="b">
-        <v>0</v>
-      </c>
+      <c r="G258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -8305,8 +8127,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-wotan-wilke-moehring-im-wahn-im-schnellcheck-a-d73f37d3-ef52-466a-83f7-5eb7ce14b980</t>
         </is>
       </c>
-      <c r="G259" t="b">
-        <v>1</v>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>2026-11-11T21:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="260">
@@ -8336,9 +8160,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenchen-zweiter-jubilaeumskrimi-im-schnellcheck-a-ce9843a2-cf0f-47f7-aebe-9b2ceb707411</t>
         </is>
       </c>
-      <c r="G260" t="b">
-        <v>0</v>
-      </c>
+      <c r="G260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -8367,8 +8189,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-heike-makatsch-aus-mainz-in-seinen-augen-im-schnellcheck-a-408979bf-95f0-45aa-b07b-d01cd918d92e</t>
         </is>
       </c>
-      <c r="G261" t="b">
-        <v>1</v>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>2026-05-25T20:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="262">
@@ -8398,9 +8222,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dortmund-inferno-mit-joerg-hartmann-im-schnellcheck-a-f0b9c417-0aab-4af2-b5ab-201349f3dbed</t>
         </is>
       </c>
-      <c r="G262" t="b">
-        <v>0</v>
-      </c>
+      <c r="G262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -8429,9 +8251,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dortmund-inferno-im-schnellcheck-a-1262309.html</t>
         </is>
       </c>
-      <c r="G263" t="b">
-        <v>0</v>
-      </c>
+      <c r="G263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -8460,9 +8280,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-zuerich-kammerflimmern-im-schnellcheck-a-fd6bbb85-2216-4464-adb8-b8664045fc45</t>
         </is>
       </c>
-      <c r="G264" t="b">
-        <v>0</v>
-      </c>
+      <c r="G264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -8491,9 +8309,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-kaputt-im-schnellcheck-a-1270850.html</t>
         </is>
       </c>
-      <c r="G265" t="b">
-        <v>0</v>
-      </c>
+      <c r="G265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -8522,8 +8338,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-kartenhaus-im-schnellcheck-a-1074503.html</t>
         </is>
       </c>
-      <c r="G266" t="b">
-        <v>1</v>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>2026-04-19T18:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="267">
@@ -8553,8 +8371,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dresden-katz-und-maus-im-schnellcheck-a-b47d7473-c95e-440c-86c7-57b6cb82bb9f</t>
         </is>
       </c>
-      <c r="G267" t="b">
-        <v>1</v>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>2026-07-27T18:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="268">
@@ -8584,8 +8404,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenchen-kehraus-im-schnellcheck-a-a2510dd7-902d-4db4-b122-f034f254b6ee</t>
         </is>
       </c>
-      <c r="G268" t="b">
-        <v>1</v>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>2026-03-04T23:20:00Z</t>
+        </is>
       </c>
     </row>
     <row r="269">
@@ -8615,9 +8437,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-kein-mitleid-keine-gnade-im-schnellcheck-a-e995cc97-5a57-4be3-a779-834b65ffe49a</t>
         </is>
       </c>
-      <c r="G269" t="b">
-        <v>0</v>
-      </c>
+      <c r="G269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -8646,8 +8466,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenchen-ki-im-schnellcheck-a-1233301.html</t>
         </is>
       </c>
-      <c r="G270" t="b">
-        <v>1</v>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>2026-03-18T20:45:00Z</t>
+        </is>
       </c>
     </row>
     <row r="271">
@@ -8677,9 +8499,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-luzern-lohnt-sich-das-einschalten-schnellcheck-a-1080308.html</t>
         </is>
       </c>
-      <c r="G271" t="b">
-        <v>0</v>
-      </c>
+      <c r="G271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -8708,8 +8528,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenchen-klingelingeling-mit-batic-und-leitmayr-im-schnellcheck-a-1126597.html</t>
         </is>
       </c>
-      <c r="G272" t="b">
-        <v>1</v>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>2026-12-02T20:45:00Z</t>
+        </is>
       </c>
     </row>
     <row r="273">
@@ -8739,9 +8561,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenchen-koeniginnen-im-schnellcheck-a-1f9b1377-a993-4db5-851b-3aa2ca452802</t>
         </is>
       </c>
-      <c r="G273" t="b">
-        <v>0</v>
-      </c>
+      <c r="G273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -8770,9 +8590,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-frankfurt-kontrollverlust-mit-brix-im-schnellcheck-a-44b0fbb8-b5d1-4268-8f71-b3dfd44d61c2</t>
         </is>
       </c>
-      <c r="G274" t="b">
-        <v>0</v>
-      </c>
+      <c r="G274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -8801,9 +8619,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-ludwigshafen-kopper-im-schnellcheck-a-1185987.html</t>
         </is>
       </c>
-      <c r="G275" t="b">
-        <v>0</v>
-      </c>
+      <c r="G275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -8832,9 +8648,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-wien-krank-im-schnellcheck-a-ed15b061-5604-464e-8bf9-0f23190063de</t>
         </is>
       </c>
-      <c r="G276" t="b">
-        <v>0</v>
-      </c>
+      <c r="G276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -8859,9 +8673,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-lindholm-krieg-im-kopf-im-schnellcheck-a-bc00137d-dece-43b4-9834-5d371bd0071e</t>
         </is>
       </c>
-      <c r="G277" t="b">
-        <v>0</v>
-      </c>
+      <c r="G277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -8890,9 +8702,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-luzern-kriegssplitter-mit-stefan-gubser-im-schnellcheck-a-1136103.html</t>
         </is>
       </c>
-      <c r="G278" t="b">
-        <v>0</v>
-      </c>
+      <c r="G278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -8921,8 +8731,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenster-lakritz-im-schnellcheck-a-1294304.html</t>
         </is>
       </c>
-      <c r="G279" t="b">
-        <v>1</v>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="280">
@@ -8952,9 +8764,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-frankfurt-land-in-dieser-zeit-im-schnellcheck-a-1128380.html</t>
         </is>
       </c>
-      <c r="G280" t="b">
-        <v>0</v>
-      </c>
+      <c r="G280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -8983,9 +8793,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-stuttgart-lassen-sie-gehen-im-schnellcheck-a-8c8fc3b9-f2f1-40d5-a757-0020d8494d89</t>
         </is>
       </c>
-      <c r="G281" t="b">
-        <v>0</v>
-      </c>
+      <c r="G281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -9014,9 +8822,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-frankfurt-leben-tod-ekstase-im-schnellcheck-a-02f07a4d-6631-4509-bdc2-b36bc771d95d</t>
         </is>
       </c>
-      <c r="G282" t="b">
-        <v>0</v>
-      </c>
+      <c r="G282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -9045,9 +8851,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-ludwigshafen-lenas-tante-im-schnellcheck-a-8ef60974-7765-4211-89a7-b752fc9af5ed</t>
         </is>
       </c>
-      <c r="G283" t="b">
-        <v>0</v>
-      </c>
+      <c r="G283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -9072,9 +8876,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-lena-odenthal-leonessa-im-schnellcheck-a-8be4457f-e0af-414c-b85b-37802c00e04d</t>
         </is>
       </c>
-      <c r="G284" t="b">
-        <v>0</v>
-      </c>
+      <c r="G284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -9099,8 +8901,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-maria-furtwaengler-letzte-ernte-im-schnellcheck-a-0fcb02c5-43f9-449a-ad6a-798fd080b0c2</t>
         </is>
       </c>
-      <c r="G285" t="b">
-        <v>1</v>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>2026-10-26T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="286">
@@ -9130,9 +8934,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-aus-dem-schwarzwald-letzter-ausflug-schauinsland-im-schnellcheck-a-234cacfd-4954-401c-9e55-6b1de82bcc74</t>
         </is>
       </c>
-      <c r="G286" t="b">
-        <v>0</v>
-      </c>
+      <c r="G286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -9161,8 +8963,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dresden-level-x-ueber-youtube-stars-im-schnellcheck-a-1150982.html</t>
         </is>
       </c>
-      <c r="G287" t="b">
-        <v>1</v>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>2026-06-10T23:25:00Z</t>
+        </is>
       </c>
     </row>
     <row r="288">
@@ -9192,8 +8996,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-frankfurt-ard-sonntagskrimi-im-schnellcheck-a-2bccbf28-db50-44a9-9054-e64c5c8534d9</t>
         </is>
       </c>
-      <c r="G288" t="b">
-        <v>1</v>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>2026-11-30T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="289">
@@ -9223,8 +9029,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dortmund-schnellcheck-zu-liebe-mich-a-157a3df4-f96f-44ea-b90a-58feff91d54e</t>
         </is>
       </c>
-      <c r="G289" t="b">
-        <v>1</v>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>2026-07-23T20:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="290">
@@ -9254,8 +9062,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-bremen-liebeswut-im-schnellcheck-a-4b927abf-adc6-4929-afd7-c67985a6ad5f</t>
         </is>
       </c>
-      <c r="G290" t="b">
-        <v>1</v>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>2026-04-22T20:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="291">
@@ -9285,8 +9095,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenster-limbus-im-schnellcheck-a-3cc946fa-96a2-47a1-a5f2-c5ba0c67c558</t>
         </is>
       </c>
-      <c r="G291" t="b">
-        <v>1</v>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>2026-12-09T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="292">
@@ -9316,8 +9128,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenster-limbus-mit-boerne-und-thiel-im-schnellcheck-a-b781b7e2-9206-4b01-9841-85be4fbc63ad</t>
         </is>
       </c>
-      <c r="G292" t="b">
-        <v>1</v>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>2026-12-09T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="293">
@@ -9347,9 +9161,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-frankfurt-luna-frisst-oder-stirbt-im-schnellcheck-a-270227de-30c1-457f-afdb-ea3a006bb172</t>
         </is>
       </c>
-      <c r="G293" t="b">
-        <v>0</v>
-      </c>
+      <c r="G293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -9378,8 +9190,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenster-magicmom-im-schnellcheck-a-ad23c832-b10f-4afe-b83a-2fcfb260f594</t>
         </is>
       </c>
-      <c r="G294" t="b">
-        <v>1</v>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>2026-11-05T21:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="295">
@@ -9409,9 +9223,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-ludwigshafen-maleficius-im-schnellcheck-a-1283814.html</t>
         </is>
       </c>
-      <c r="G295" t="b">
-        <v>0</v>
-      </c>
+      <c r="G295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -9440,8 +9252,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenster-man-stirbt-nur-zweimal-im-schnellcheck-a-f5d79c6a-4388-40cb-a9e5-6e13399e21d7</t>
         </is>
       </c>
-      <c r="G296" t="b">
-        <v>1</v>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>2026-12-20T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="297">
@@ -9471,9 +9285,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-ludwigshafen-marlon-im-schnellcheck-a-0fa768d3-9cb7-4e97-894b-dce116f87dba</t>
         </is>
       </c>
-      <c r="G297" t="b">
-        <v>0</v>
-      </c>
+      <c r="G297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -9502,9 +9314,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dortmund-masken-im-schnellcheck-a-9d1456d8-0c39-4637-8b71-b4ce913acaae</t>
         </is>
       </c>
-      <c r="G298" t="b">
-        <v>0</v>
-      </c>
+      <c r="G298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -9533,9 +9343,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-wien-messer-mit-eisner-und-fellner-im-schnellcheck-a-c6183575-9b81-41a3-ae3f-4a0ca6285051</t>
         </is>
       </c>
-      <c r="G299" t="b">
-        <v>0</v>
-      </c>
+      <c r="G299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -9564,9 +9372,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-berlin-meta-mit-karow-und-rubin-im-schnellcheck-a-1192696.html</t>
         </is>
       </c>
-      <c r="G300" t="b">
-        <v>0</v>
-      </c>
+      <c r="G300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -9595,9 +9401,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-aus-muenchen-mit-den-kommissaren-batic-und-leitmayr-im-schnellcheck-a-1084792.html</t>
         </is>
       </c>
-      <c r="G301" t="b">
-        <v>0</v>
-      </c>
+      <c r="G301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -9626,8 +9430,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-mitgehangen-im-schnellcheck-a-1197366.html</t>
         </is>
       </c>
-      <c r="G302" t="b">
-        <v>1</v>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>2026-06-17T18:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="303">
@@ -9657,9 +9463,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dortmund-monster-im-schnellcheck-a-2a4e24e6-9e67-458b-883b-bcdbf25d6d53</t>
         </is>
       </c>
-      <c r="G303" t="b">
-        <v>0</v>
-      </c>
+      <c r="G303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -9684,8 +9488,10 @@
           <t>https://www.spiegel.de/kultur/tv/wunsch-tatort-heute-mord-auf-langeoog-im-schnellcheck-a-2a8a9c65-c1df-4c22-a352-f231674fa8e2</t>
         </is>
       </c>
-      <c r="G304" t="b">
-        <v>1</v>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>2027-01-10T20:45:00Z</t>
+        </is>
       </c>
     </row>
     <row r="305">
@@ -9715,9 +9521,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dem-saarland-mord-ex-machina-im-schnellcheck-a-1183553.html</t>
         </is>
       </c>
-      <c r="G305" t="b">
-        <v>0</v>
-      </c>
+      <c r="G305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -9746,8 +9550,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenchen-mord-unter-misteln-im-schnellcheck-a-ef90ff50-3bee-4c08-9d62-bf507e0acfa4</t>
         </is>
       </c>
-      <c r="G306" t="b">
-        <v>1</v>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>2026-12-16T22:30:00Z</t>
+        </is>
       </c>
     </row>
     <row r="307">
@@ -9773,8 +9579,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-ulrich-tukur-murot-und-das-1000-jaehrige-reich-im-schnellcheck-a-f52088fc-d88c-4e90-903f-5882ff9adbd1</t>
         </is>
       </c>
-      <c r="G307" t="b">
-        <v>1</v>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>2026-02-23T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="308">
@@ -9800,8 +9608,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-ulrich-tukur-murot-und-das-gesetz-des-karma-im-schnellcheck-a-efc022c8-3242-4aa0-acca-4de7e869b751</t>
         </is>
       </c>
-      <c r="G308" t="b">
-        <v>1</v>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>2026-04-28T09:03:57.008Z</t>
+        </is>
       </c>
     </row>
     <row r="309">
@@ -9827,8 +9637,10 @@
           <t>https://www.spiegel.de/kultur/tatort-heute-mit-ulrich-tukur-murot-sucht-das-glueck-im-schnellcheck-a-d162db50-747e-4f85-af52-f8745b9454ba</t>
         </is>
       </c>
-      <c r="G309" t="b">
-        <v>1</v>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>2026-11-10T11:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="310">
@@ -9854,8 +9666,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-ulrich-tukur-murot-und-das-prinzip-hoffnung-im-schnellcheck-a-fdf23731-8afe-45da-9441-8ea539b1d292</t>
         </is>
       </c>
-      <c r="G310" t="b">
-        <v>1</v>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>2026-12-09T21:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="311">
@@ -9881,8 +9695,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-ulrich-tukur-murot-und-der-elefant-im-raum-im-schnellcheck-a-a51d2767-e018-4a86-83d3-72ac8d89d8b2</t>
         </is>
       </c>
-      <c r="G311" t="b">
-        <v>1</v>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>2026-12-28T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="312">
@@ -9912,9 +9728,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-nachbarn-mit-ballauf-und-schenk-im-schnellcheck-a-1139142.html</t>
         </is>
       </c>
-      <c r="G312" t="b">
-        <v>0</v>
-      </c>
+      <c r="G312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -9943,8 +9757,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dresden-nachtschatten-im-schnellcheck-a-190c67c5-8cf5-4bca-9c96-1cf62f5cd572</t>
         </is>
       </c>
-      <c r="G313" t="b">
-        <v>1</v>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>2027-01-02T00:35:00Z</t>
+        </is>
       </c>
     </row>
     <row r="314">
@@ -9974,9 +9790,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-bremen-nachtsicht-ueber-geisterfahrer-mit-sabine-postel-a-1137163.html</t>
         </is>
       </c>
-      <c r="G314" t="b">
-        <v>0</v>
-      </c>
+      <c r="G314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -10005,9 +9819,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-narben-im-schnellcheck-a-1089358.html</t>
         </is>
       </c>
-      <c r="G315" t="b">
-        <v>0</v>
-      </c>
+      <c r="G315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -10036,8 +9848,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-mit-lindholm-national-feminin-im-schnellcheck-a-b98f1ce3-99ed-4aee-ad66-8124372790bd</t>
         </is>
       </c>
-      <c r="G316" t="b">
-        <v>1</v>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>2027-01-06T21:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="317">
@@ -10067,8 +9881,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dresden-nemesis-im-schnellcheck-a-1279894.html</t>
         </is>
       </c>
-      <c r="G317" t="b">
-        <v>1</v>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>2026-11-17T21:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="318">
@@ -10098,8 +9914,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-bremen-mit-jasna-fritzi-bauer-neugeboren-im-schnellcheck-a-567ae28b-0712-43f7-a260-7b3d7107e440</t>
         </is>
       </c>
-      <c r="G318" t="b">
-        <v>1</v>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>2026-06-18T20:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="319">
@@ -10129,9 +9947,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-berlin-nichts-als-die-wahrheit-mit-harfouch-und-waschke-im-schnellcheck-a-52fd7174-fc70-4d8e-a553-e0bf78b95ed3</t>
         </is>
       </c>
-      <c r="G319" t="b">
-        <v>0</v>
-      </c>
+      <c r="G319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -10160,9 +9976,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-niemals-ohne-mich-im-schnellcheck-a-f8bfda4a-7fa7-4581-a71d-a5a00eb33e07</t>
         </is>
       </c>
-      <c r="G320" t="b">
-        <v>0</v>
-      </c>
+      <c r="G320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -10191,9 +10005,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-aus-muenchen-one-way-ticket-im-schnellcheck-a-1296721.html</t>
         </is>
       </c>
-      <c r="G321" t="b">
-        <v>0</v>
-      </c>
+      <c r="G321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -10222,8 +10034,10 @@
           <t>https://www.spiegel.de/kultur/tatort-heute-aus-dresden-parasomnia-im-schnellcheck-a-b363237f-03d5-4f73-b46c-73bed85df24c</t>
         </is>
       </c>
-      <c r="G322" t="b">
-        <v>1</v>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>2026-11-05T21:10:00Z</t>
+        </is>
       </c>
     </row>
     <row r="323">
@@ -10253,8 +10067,10 @@
           <t>https://www.spiegel.de/kultur/tatort-heute-aus-dresden-parasomnia-im-schnellcheck-a-bfe1b8ce-6ca4-4d13-9f8e-c7de13740b50</t>
         </is>
       </c>
-      <c r="G323" t="b">
-        <v>1</v>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>2026-11-05T21:10:00Z</t>
+        </is>
       </c>
     </row>
     <row r="324">
@@ -10284,8 +10100,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenster-propheteus-im-schnellcheck-a-d42eb8fa-36ff-41a3-851d-fcf8e4c32685</t>
         </is>
       </c>
-      <c r="G324" t="b">
-        <v>1</v>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>2026-07-15T18:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="325">
@@ -10315,9 +10133,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-pyramide-im-schnellcheck-a-695b405e-9346-4004-b625-05df864b1715</t>
         </is>
       </c>
-      <c r="G325" t="b">
-        <v>0</v>
-      </c>
+      <c r="G325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -10342,8 +10158,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-wotan-wilke-moehring-querschlaeger-im-schnellcheck-a-9a316990-4519-4c95-a8a2-ed4f30b30f02</t>
         </is>
       </c>
-      <c r="G326" t="b">
-        <v>1</v>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>2026-02-15T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="327">
@@ -10369,8 +10187,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-wotan-wilke-moehring-querschlaeger-im-schnellcheck-a-1297996.html</t>
         </is>
       </c>
-      <c r="G327" t="b">
-        <v>1</v>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>2026-02-15T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="328">
@@ -10400,9 +10220,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-zuerich-rapunzel-im-schnellcheck-a-8c8ec235-b280-4afd-b37e-e0cde945097e</t>
         </is>
       </c>
-      <c r="G328" t="b">
-        <v>0</v>
-      </c>
+      <c r="G328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -10431,9 +10249,7 @@
           <t>https://www.spiegel.de/kultur/tatort-heute-aus-dem-schwarzwald-rebland-im-schnellcheck-a-43e04263-048d-4bef-aecc-2f87fc7161ba</t>
         </is>
       </c>
-      <c r="G329" t="b">
-        <v>0</v>
-      </c>
+      <c r="G329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -10458,9 +10274,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-mit-maria-simon-heimatliebe-im-schnellcheck-a-1281319.html</t>
         </is>
       </c>
-      <c r="G330" t="b">
-        <v>0</v>
-      </c>
+      <c r="G330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -10489,9 +10303,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-restschuld-im-schnellcheck-a-1268c1af-9213-444d-a862-abf50c23322a</t>
         </is>
       </c>
-      <c r="G331" t="b">
-        <v>0</v>
-      </c>
+      <c r="G331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -10520,8 +10332,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dresden-rettung-so-nah-im-schnellcheck-a-4c4292e0-99e5-41e0-9cab-08e57082678a</t>
         </is>
       </c>
-      <c r="G332" t="b">
-        <v>1</v>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>2027-01-07T21:10:00Z</t>
+        </is>
       </c>
     </row>
     <row r="333">
@@ -10551,8 +10365,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenster-rhythm-and-love-mit-jan-josef-liefers-im-schnellcheck-a-e0ec4a2b-e3d9-4bf4-906a-52943c27e2d4</t>
         </is>
       </c>
-      <c r="G333" t="b">
-        <v>1</v>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>2026-12-02T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="334">
@@ -10582,9 +10398,7 @@
           <t>https://www.spiegel.de/kultur/tatort-heute-aus-zuerich-risiko-mit-nebenwirkungen-im-schnellcheck-a-0b4779e7-06b4-412d-aa49-e49e07837960</t>
         </is>
       </c>
-      <c r="G334" t="b">
-        <v>0</v>
-      </c>
+      <c r="G334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -10613,9 +10427,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-stuttgart-rote-schatten-im-schnellcheck-a-1172411.html</t>
         </is>
       </c>
-      <c r="G335" t="b">
-        <v>0</v>
-      </c>
+      <c r="G335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -10644,9 +10456,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dem-schwarzwald-saras-gestaendnis-im-schnellcheck-a-ac9df4e1-d92b-4fb2-8dde-9a4db12762df</t>
         </is>
       </c>
-      <c r="G336" t="b">
-        <v>0</v>
-      </c>
+      <c r="G336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -10675,9 +10485,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-zuerich-schattenkinder-im-schnellcheck-a-0d5a3caa-133b-41a8-af94-bf4873bf97fc</t>
         </is>
       </c>
-      <c r="G337" t="b">
-        <v>0</v>
-      </c>
+      <c r="G337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -10706,9 +10514,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-hamburg-mit-wotan-wilke-moehring-schattenleben-im-schnellcheck-a-f1e987b9-2622-4a69-8e57-e58f86132507</t>
         </is>
       </c>
-      <c r="G338" t="b">
-        <v>0</v>
-      </c>
+      <c r="G338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -10737,8 +10543,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenchen-schau-mich-an-im-schnellcheck-a-d6245824-8040-44c0-8da1-f34ceba6e0a8</t>
         </is>
       </c>
-      <c r="G339" t="b">
-        <v>1</v>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>2026-03-25T20:45:00Z</t>
+        </is>
       </c>
     </row>
     <row r="340">
@@ -10768,9 +10576,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenster-schlangengrube-im-schnellcheck-a-1208737.html</t>
         </is>
       </c>
-      <c r="G340" t="b">
-        <v>0</v>
-      </c>
+      <c r="G340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -10799,9 +10605,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-wien-schock-mit-harald-krassnitzer-im-schnellcheck-a-1130408.html</t>
         </is>
       </c>
-      <c r="G341" t="b">
-        <v>0</v>
-      </c>
+      <c r="G341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -10830,9 +10634,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-zuerich-schoggilaebe-im-schnellcheck-a-af785cbd-73a4-4a35-8cab-9374d7be6369</t>
         </is>
       </c>
-      <c r="G342" t="b">
-        <v>0</v>
-      </c>
+      <c r="G342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -10861,8 +10663,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-schutzmassnahmen-im-schnellcheck-a-caf27312-e797-4ae2-8a9f-3a5471f915db</t>
         </is>
       </c>
-      <c r="G343" t="b">
-        <v>1</v>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>2026-06-06T20:20:00Z</t>
+        </is>
       </c>
     </row>
     <row r="344">
@@ -10888,8 +10692,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-wotan-wilke-moehring-schweigen-im-schnellcheck-a-5321b61c-cbbf-4380-a6c3-7756dc15753f</t>
         </is>
       </c>
-      <c r="G344" t="b">
-        <v>1</v>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>2026-02-09T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="345">
@@ -10919,9 +10725,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-zuerich-seilschaft-im-schnellcheck-a-0eca10fe-b525-4bb2-9fa6-b350e0d84b20</t>
         </is>
       </c>
-      <c r="G345" t="b">
-        <v>0</v>
-      </c>
+      <c r="G345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -10950,8 +10754,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dresden-siebenschlaefer-im-schnellcheck-a-2b3dcbc0-f061-4014-9972-7a1c2b2b7fb8</t>
         </is>
       </c>
-      <c r="G346" t="b">
-        <v>1</v>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:45:00Z</t>
+        </is>
       </c>
     </row>
     <row r="347">
@@ -10981,8 +10787,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-siebte-etage-im-schnellcheck-a-fb850800-7cbc-49d0-acdc-8222a1790cc5</t>
         </is>
       </c>
-      <c r="G347" t="b">
-        <v>1</v>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>2026-10-11T18:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="348">
@@ -11012,9 +10820,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dem-saarland-soehne-und-vaeter-mit-devid-striesow-im-schnellcheck-a-1131896.html</t>
         </is>
       </c>
-      <c r="G348" t="b">
-        <v>0</v>
-      </c>
+      <c r="G348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -11043,8 +10849,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-bremen-solange-du-atmest-im-schnellcheck-a-1cd36db9-0c73-44fa-b137-f9723d590e84</t>
         </is>
       </c>
-      <c r="G349" t="b">
-        <v>1</v>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>2026-05-11T18:14:00Z</t>
+        </is>
       </c>
     </row>
     <row r="350">
@@ -11074,8 +10882,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dem-schwarzwald-sonnenwende-im-schnellcheck-a-1204881.html</t>
         </is>
       </c>
-      <c r="G350" t="b">
-        <v>1</v>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>2026-03-08T04:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="351">
@@ -11105,8 +10915,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenster-spieglein-spieglein-im-schnellcheck-a-1257463.html</t>
         </is>
       </c>
-      <c r="G351" t="b">
-        <v>1</v>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>2026-09-23T18:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="352">
@@ -11136,9 +10948,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-spur-des-blutes-im-schnellcheck-a-0c117c6d-b6ea-42d5-8c88-8185bad5463c</t>
         </is>
       </c>
-      <c r="G352" t="b">
-        <v>0</v>
-      </c>
+      <c r="G352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -11167,9 +10977,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-stuttgart-stau-im-schnellcheck-a-1166361.html</t>
         </is>
       </c>
-      <c r="G353" t="b">
-        <v>0</v>
-      </c>
+      <c r="G353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -11198,9 +11006,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-wien-sternschnuppe-im-check-a-1072832.html</t>
         </is>
       </c>
-      <c r="G354" t="b">
-        <v>0</v>
-      </c>
+      <c r="G354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -11229,9 +11035,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-bremen-stille-nacht-im-schnellcheck-a-ea228f3a-546c-4eef-b491-7a2d1669972f</t>
         </is>
       </c>
-      <c r="G355" t="b">
-        <v>0</v>
-      </c>
+      <c r="G355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -11260,9 +11064,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dortmund-sturm-mit-peter-faber-im-schnellcheck-a-1126266.html</t>
         </is>
       </c>
-      <c r="G356" t="b">
-        <v>0</v>
-      </c>
+      <c r="G356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -11291,8 +11093,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-tanzmariechen-ueber-den-karneval-im-schnellcheck-a-1134827.html</t>
         </is>
       </c>
-      <c r="G357" t="b">
-        <v>1</v>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>2026-02-23T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="358">
@@ -11322,9 +11126,7 @@
           <t>https://www.spiegel.de/kultur/tv/polizeiruf-110-heute-aus-magdeburg-zehn-rosen-im-schnellcheck-a-1249201.html</t>
         </is>
       </c>
-      <c r="G358" t="b">
-        <v>0</v>
-      </c>
+      <c r="G358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -11349,9 +11151,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-taxi-nach-leipzig-der-1000-tatort-im-schnellcheck-a-1119647.html</t>
         </is>
       </c>
-      <c r="G359" t="b">
-        <v>0</v>
-      </c>
+      <c r="G359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -11380,8 +11180,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-aus-berlin-tiere-der-grossstadt-im-schnellcheck-a-1225675.html</t>
         </is>
       </c>
-      <c r="G360" t="b">
-        <v>1</v>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>2026-02-17T22:59:59Z</t>
+        </is>
       </c>
     </row>
     <row r="361">
@@ -11411,8 +11213,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-berlin-tiere-der-grossstadt-im-schnellcheck-a-a26712ac-f94e-4a4d-8a10-80e8a06b2479</t>
         </is>
       </c>
-      <c r="G361" t="b">
-        <v>1</v>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>2026-02-17T22:59:59Z</t>
+        </is>
       </c>
     </row>
     <row r="362">
@@ -11442,9 +11246,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dortmund-tod-und-spiele-schnellcheck-a-1226917.html</t>
         </is>
       </c>
-      <c r="G362" t="b">
-        <v>0</v>
-      </c>
+      <c r="G362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -11473,8 +11275,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dortmund-tollwut-im-schnellcheck-mit-joerg-hartmann-a-3eb64eac-e421-48fc-8ea8-5688fcf2da83</t>
         </is>
       </c>
-      <c r="G363" t="b">
-        <v>1</v>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>2027-01-06T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="364">
@@ -11504,8 +11308,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dortmund-tollwut-im-schnellcheck-a-1190079.html</t>
         </is>
       </c>
-      <c r="G364" t="b">
-        <v>1</v>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>2027-01-06T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="365">
@@ -11535,9 +11341,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-saarbruecken-totenstille-im-check-a-1071685.html</t>
         </is>
       </c>
-      <c r="G365" t="b">
-        <v>0</v>
-      </c>
+      <c r="G365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -11566,8 +11370,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dresden-totes-herz-im-schnellcheck-a-f4d12702-8c87-456e-8831-88ea3e3b4d0b</t>
         </is>
       </c>
-      <c r="G366" t="b">
-        <v>1</v>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>2026-08-08T20:20:00Z</t>
+        </is>
       </c>
     </row>
     <row r="367">
@@ -11593,9 +11399,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-kommissar-treibjagd-im-schnellcheck-treibjagd-im-schnellcheck-a-1237556.html</t>
         </is>
       </c>
-      <c r="G367" t="b">
-        <v>0</v>
-      </c>
+      <c r="G367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -11624,8 +11428,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-franken-trotzdem-mit-dagmar-manzel-im-schnellcheck-a-224c2a90-387f-4cff-90c6-9f57d96b4884</t>
         </is>
       </c>
-      <c r="G368" t="b">
-        <v>1</v>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>2026-04-15T19:45:00Z</t>
+        </is>
       </c>
     </row>
     <row r="369">
@@ -11651,8 +11457,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-til-schweiger-tschill-out-im-schnellcheck-a-1303230.html</t>
         </is>
       </c>
-      <c r="G369" t="b">
-        <v>1</v>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>2026-09-17T20:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="370">
@@ -11678,9 +11486,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-tschiller-off-duty-mit-til-schweiger-im-schnellcheck-a-1215830.html</t>
         </is>
       </c>
-      <c r="G370" t="b">
-        <v>0</v>
-      </c>
+      <c r="G370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -11705,9 +11511,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-ulrich-tukur-murot-und-das-murmeltier-im-schnellcheck-a-1252623.html</t>
         </is>
       </c>
-      <c r="G371" t="b">
-        <v>0</v>
-      </c>
+      <c r="G371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -11732,8 +11536,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-wotan-wilke-moehring-tyrannenmord-im-schnellcheck-a-4670e252-c7aa-4a80-9b44-a12c01e04b6e</t>
         </is>
       </c>
-      <c r="G372" t="b">
-        <v>1</v>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>2026-05-27T20:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="373">
@@ -11763,8 +11569,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-stuttgart-ueberlebe-wenigstens-bis-morgen-im-schnellcheck-a-8d34d07e-5ab7-4f0d-98af-1c3b24fe355a</t>
         </is>
       </c>
-      <c r="G373" t="b">
-        <v>1</v>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>2026-11-23T18:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="374">
@@ -11794,8 +11602,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-bremen-und-immer-gewinnt-die-nacht-im-schnellcheck-a-d5cc0f84-98bc-496e-9319-1a24f1bd0cff</t>
         </is>
       </c>
-      <c r="G374" t="b">
-        <v>1</v>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>2026-05-19T20:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="375">
@@ -11825,8 +11635,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenchen-unklare-lage-im-schnellcheck-a-130f4d6e-f3c2-4d99-a612-a2fe3e29e58b</t>
         </is>
       </c>
-      <c r="G375" t="b">
-        <v>1</v>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>2026-02-19T20:45:00Z</t>
+        </is>
       </c>
     </row>
     <row r="376">
@@ -11856,8 +11668,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dresden-unsichtbar-im-schnellcheck-a-d7918d4a-1590-4c92-9a35-9b10c6df06d0</t>
         </is>
       </c>
-      <c r="G376" t="b">
-        <v>1</v>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>2026-10-22T20:10:00Z</t>
+        </is>
       </c>
     </row>
     <row r="377">
@@ -11887,9 +11701,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dem-schwarzwald-unten-im-tal-im-schnellcheck-a-b8fcd5ce-1274-44be-8876-32d485701908</t>
         </is>
       </c>
-      <c r="G377" t="b">
-        <v>0</v>
-      </c>
+      <c r="G377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -11918,8 +11730,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dresden-unter-feuer-im-schnellcheck-a-f09c81db-c293-4fce-a50b-cd7dc426f4cf</t>
         </is>
       </c>
-      <c r="G378" t="b">
-        <v>1</v>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>2026-07-09T20:10:00Z</t>
+        </is>
       </c>
     </row>
     <row r="379">
@@ -11949,9 +11763,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenster-unter-gaertnern-im-schnellcheck-a-006f9b3c-1299-44b7-8ab6-a9ff7407268e</t>
         </is>
       </c>
-      <c r="G379" t="b">
-        <v>0</v>
-      </c>
+      <c r="G379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -11980,9 +11792,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-aus-frankfurt-unter-kriegern-im-schnellcheck-a-1199968.html</t>
         </is>
       </c>
-      <c r="G380" t="b">
-        <v>0</v>
-      </c>
+      <c r="G380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -12011,8 +11821,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenster-vaeterchen-rost-im-schnellcheck-a-1299567.html</t>
         </is>
       </c>
-      <c r="G381" t="b">
-        <v>1</v>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>2026-12-25T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="382">
@@ -12042,8 +11854,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-stuttgart-verblendung-im-schnellcheck-a-83fa33e9-9c1d-412d-8fd4-71e3776812e6</t>
         </is>
       </c>
-      <c r="G382" t="b">
-        <v>1</v>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>2027-01-07T04:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="383">
@@ -12069,8 +11883,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-falke-und-grosz-verborgen-im-schnellcheck-a-9552bb5f-33fa-4fe1-9e47-e8f09753c8f0</t>
         </is>
       </c>
-      <c r="G383" t="b">
-        <v>1</v>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>2026-03-28T21:20:00Z</t>
+        </is>
       </c>
     </row>
     <row r="384">
@@ -12100,9 +11916,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-kiel-borowski-und-das-fest-des-nordens-im-schnellcheck-a-1152238.html</t>
         </is>
       </c>
-      <c r="G384" t="b">
-        <v>0</v>
-      </c>
+      <c r="G384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -12133,9 +11947,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-wien-verschwoerung-im-schnellcheck-a-e4ba072f-fb57-463d-888b-828b2b484e6b</t>
         </is>
       </c>
-      <c r="G385" t="b">
-        <v>0</v>
-      </c>
+      <c r="G385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -12164,8 +11976,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-vier-jahre-im-schnellcheck-a-311061a4-57ea-4084-a47b-7378a91aec3b</t>
         </is>
       </c>
-      <c r="G386" t="b">
-        <v>1</v>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>2026-12-30T19:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="387">
@@ -12195,8 +12009,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-berlin-vier-leben-im-schnellcheck-a-d78981c8-6b7b-46cc-91f2-73fc48939f71</t>
         </is>
       </c>
-      <c r="G387" t="b">
-        <v>1</v>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>2026-09-29T21:59:59Z</t>
+        </is>
       </c>
     </row>
     <row r="388">
@@ -12226,9 +12042,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-aus-wien-virus-mit-moritz-eisner-und-bibi-fellner-im-schnellcheck-a-1163743.html</t>
         </is>
       </c>
-      <c r="G388" t="b">
-        <v>0</v>
-      </c>
+      <c r="G388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -12257,9 +12071,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-ludwigshafen-vom-himmel-hoch-im-schnellcheck-a-1241813.html</t>
         </is>
       </c>
-      <c r="G389" t="b">
-        <v>0</v>
-      </c>
+      <c r="G389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -12288,9 +12100,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-zuerich-von-affen-und-menschen-im-schnellcheck-a-62534606-3eb8-458e-98e9-d9b268943045</t>
         </is>
       </c>
-      <c r="G390" t="b">
-        <v>0</v>
-      </c>
+      <c r="G390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -12319,9 +12129,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-wacht-am-rhein-im-schnellcheck-a-1128925.html</t>
         </is>
       </c>
-      <c r="G391" t="b">
-        <v>0</v>
-      </c>
+      <c r="G391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -12350,9 +12158,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-wien-wahre-luegen-im-schnellcheck-a-1247074.html</t>
         </is>
       </c>
-      <c r="G392" t="b">
-        <v>0</v>
-      </c>
+      <c r="G392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -12381,9 +12187,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-ludwigshafen-waldlust-im-schnellcheck-a-1195486.html</t>
         </is>
       </c>
-      <c r="G393" t="b">
-        <v>0</v>
-      </c>
+      <c r="G393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -12412,8 +12216,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-franken-warum-im-schnellcheck-a-df8c2147-5b23-463d-b0c2-c838d03d6392</t>
         </is>
       </c>
-      <c r="G394" t="b">
-        <v>1</v>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>2026-09-16T19:45:00Z</t>
+        </is>
       </c>
     </row>
     <row r="395">
@@ -12443,8 +12249,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-franken-warum-im-schnellcheck-a-17dfde33-a363-4391-a15d-ecbab39b409e</t>
         </is>
       </c>
-      <c r="G395" t="b">
-        <v>1</v>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>2026-09-16T19:45:00Z</t>
+        </is>
       </c>
     </row>
     <row r="396">
@@ -12470,8 +12278,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-falke-und-grosz-was-bleibt-im-schnellcheck-a-0a5b3356-f549-448e-a130-8ddbc2065b35</t>
         </is>
       </c>
-      <c r="G396" t="b">
-        <v>1</v>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>2026-07-13T18:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="397">
@@ -12501,9 +12311,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-wien-was-ist-das-fuer-eine-welt-im-schnellcheck-a-b532b4f0-899c-443a-a124-c4500d39df3a</t>
         </is>
       </c>
-      <c r="G397" t="b">
-        <v>0</v>
-      </c>
+      <c r="G397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -12532,8 +12340,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dem-schwarzwald-was-wir-erben-im-schnellcheck-a-552e9e77-5e74-4212-a0d9-e4b1493e7c3a</t>
         </is>
       </c>
-      <c r="G398" t="b">
-        <v>1</v>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>2026-04-19T18:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="399">
@@ -12563,8 +12373,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-was-wir-erben-aus-freiburg-ein-krimi-so-mitreissend-wie-eine-sitzung-beim-notar-a-8a522030-60f2-4d1d-a4e3-ccbf05ac678d</t>
         </is>
       </c>
-      <c r="G399" t="b">
-        <v>1</v>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>2026-04-19T18:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="400">
@@ -12594,9 +12406,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-wien-wehrlos-mit-fellner-und-eisner-im-schnellcheck-a-1143389.html</t>
         </is>
       </c>
-      <c r="G400" t="b">
-        <v>0</v>
-      </c>
+      <c r="G400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -12625,8 +12435,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-weiter-immer-weiter-im-schnellcheck-a-1245773.html</t>
         </is>
       </c>
-      <c r="G401" t="b">
-        <v>1</v>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>2026-04-29T18:15:00Z</t>
+        </is>
       </c>
     </row>
     <row r="402">
@@ -12656,8 +12468,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-frankfurt-wendehammer-im-schnellcheck-a-1125592.html</t>
         </is>
       </c>
-      <c r="G402" t="b">
-        <v>1</v>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>2026-09-03T21:30:00Z</t>
+        </is>
       </c>
     </row>
     <row r="403">
@@ -12687,8 +12501,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dresden-wer-jetzt-allein-ist-im-schnellcheck-a-1205221.html</t>
         </is>
       </c>
-      <c r="G403" t="b">
-        <v>1</v>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>2026-05-21T20:10:00Z</t>
+        </is>
       </c>
     </row>
     <row r="404">
@@ -12718,8 +12534,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-frankfurt-wer-zoegert-ist-tot-im-schnellcheck-a-29ef1911-1087-43b2-b500-a8e9c2f1acbc</t>
         </is>
       </c>
-      <c r="G404" t="b">
-        <v>1</v>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:59:00Z</t>
+        </is>
       </c>
     </row>
     <row r="405">
@@ -12749,9 +12567,7 @@
           <t>https://www.spiegel.de/kultur/tatort-heute-aus-koeln-wie-alle-anderen-auch-im-schnellcheck-a-39310cb8-2b40-478b-82fb-7980ba566086</t>
         </is>
       </c>
-      <c r="G405" t="b">
-        <v>0</v>
-      </c>
+      <c r="G405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -12780,9 +12596,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-koeln-wie-alle-anderen-auch-im-schnellcheck-a-73c6b29d-affe-44f5-a568-321bab13611d</t>
         </is>
       </c>
-      <c r="G406" t="b">
-        <v>0</v>
-      </c>
+      <c r="G406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -12811,9 +12625,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-berlin-wir-ihr-sie-im-schnellcheck-a-1095515.html</t>
         </is>
       </c>
-      <c r="G407" t="b">
-        <v>0</v>
-      </c>
+      <c r="G407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -12842,8 +12654,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenchen-wir-kriegen-euch-alle-im-schnellcheck-a-1239897.html</t>
         </is>
       </c>
-      <c r="G408" t="b">
-        <v>1</v>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>2026-12-30T21:00:00Z</t>
+        </is>
       </c>
     </row>
     <row r="409">
@@ -12873,9 +12687,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-wien-wir-sind-nicht-zu-fassen-im-schnellcheck-a-166d5b08-96c9-4027-9567-d36e2b3f6425</t>
         </is>
       </c>
-      <c r="G409" t="b">
-        <v>0</v>
-      </c>
+      <c r="G409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -12904,9 +12716,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-franken-wo-ist-mike-im-schnellcheck-a-4ab50594-b009-4d1c-b094-c79f95e5f350</t>
         </is>
       </c>
-      <c r="G410" t="b">
-        <v>0</v>
-      </c>
+      <c r="G410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -12935,8 +12745,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-bremen-wo-ist-nur-mein-schatz-geblieben-im-schnellcheck-a-1263460.html</t>
         </is>
       </c>
-      <c r="G411" t="b">
-        <v>1</v>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:59:00Z</t>
+        </is>
       </c>
     </row>
     <row r="412">
@@ -12966,9 +12778,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-konstanz-wofuer-es-sich-zu-leben-lohnt-im-schnellcheck-a-1123088.html</t>
         </is>
       </c>
-      <c r="G412" t="b">
-        <v>0</v>
-      </c>
+      <c r="G412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -12997,9 +12807,7 @@
           <t>https://www.spiegel.de/kultur/tv/der-tatort-aus-muenchen-mit-batic-und-leitmayr-im-schnellcheck-a-780fa140-f67d-4354-a338-3afe21c8ca03</t>
         </is>
       </c>
-      <c r="G413" t="b">
-        <v>0</v>
-      </c>
+      <c r="G413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -13028,9 +12836,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dortmund-zahltag-im-schnellcheck-a-1115339.html</t>
         </is>
       </c>
-      <c r="G414" t="b">
-        <v>0</v>
-      </c>
+      <c r="G414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -13055,9 +12861,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-heike-makatsch-zeit-der-froesche-im-schnellcheck-a-1199024.html</t>
         </is>
       </c>
-      <c r="G415" t="b">
-        <v>0</v>
-      </c>
+      <c r="G415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -13086,9 +12890,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-stuttgart-zerrissen-im-schnellcheck-a-550092c6-b8c4-4fe8-aeee-24dc5c7d776f</t>
         </is>
       </c>
-      <c r="G416" t="b">
-        <v>0</v>
-      </c>
+      <c r="G416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -13117,9 +12919,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-dortmund-zorn-im-schnellcheck-a-1247078.html</t>
         </is>
       </c>
-      <c r="G417" t="b">
-        <v>0</v>
-      </c>
+      <c r="G417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -13144,9 +12944,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-mit-falke-erstmals-mit-franziska-weisz-schnellcheck-a-1082962.html</t>
         </is>
       </c>
-      <c r="G418" t="b">
-        <v>0</v>
-      </c>
+      <c r="G418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -13175,8 +12973,10 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-muenchen-zugzwang-im-schnellcheck-a-96362615-a205-458a-88f6-662fdd673c66</t>
         </is>
       </c>
-      <c r="G419" t="b">
-        <v>1</v>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>2026-12-30T20:45:00Z</t>
+        </is>
       </c>
     </row>
     <row r="420">
@@ -13206,9 +13006,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-zuerich-zueri-braennt-im-schnellcheck-a-ccdf7207-660c-4807-930a-bdf432437c4c</t>
         </is>
       </c>
-      <c r="G420" t="b">
-        <v>0</v>
-      </c>
+      <c r="G420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -13237,9 +13035,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-bremen-zurueck-ans-licht-im-schnellcheck-a-1171368.html</t>
         </is>
       </c>
-      <c r="G421" t="b">
-        <v>0</v>
-      </c>
+      <c r="G421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -13268,9 +13064,7 @@
           <t>https://www.spiegel.de/kultur/tv/tatort-heute-aus-der-schweiz-zwei-leben-im-schnellcheck-a-1167161.html</t>
         </is>
       </c>
-      <c r="G422" t="b">
-        <v>0</v>
-      </c>
+      <c r="G422" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tatort_verfuegbarkeit.xlsx
+++ b/tatort_verfuegbarkeit.xlsx
@@ -5804,7 +5804,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-01-27T22:59:00Z</t>
+          <t>2027-01-21T22:59:00Z</t>
         </is>
       </c>
     </row>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-01-27T22:59:00Z</t>
+          <t>2027-01-21T22:59:00Z</t>
         </is>
       </c>
     </row>
